--- a/data_indexpoints_tidy/tallmateriale_960.xlsx
+++ b/data_indexpoints_tidy/tallmateriale_960.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Programmering\R\byindeks\data_indexpoints_tidy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84FD83B-DA2E-4423-B62F-9611B9783EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EFBED0-58DE-4057-ACFC-620D75D1DC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="punkt_adt" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="533">
   <si>
     <t>trp_id</t>
   </si>
@@ -1091,7 +1091,7 @@
     <t>2025-2026</t>
   </si>
   <si>
-    <t>jan-feb</t>
+    <t>jan-mar</t>
   </si>
   <si>
     <t>2019-2021</t>
@@ -1124,7 +1124,7 @@
     <t>year_to_date</t>
   </si>
   <si>
-    <t>Februar</t>
+    <t>Mars</t>
   </si>
   <si>
     <t>2019-2026</t>
@@ -1340,6 +1340,9 @@
     <t>2019 - (mar 2025 - feb 2026)</t>
   </si>
   <si>
+    <t>2019 - (apr 2025 - mar 2026)</t>
+  </si>
+  <si>
     <t>2019 - (jan 2020 - des 2021)</t>
   </si>
   <si>
@@ -1496,6 +1499,9 @@
     <t>2019 - (mar 2024 - feb 2026)</t>
   </si>
   <si>
+    <t>2019 - (apr 2024 - mar 2026)</t>
+  </si>
+  <si>
     <t>2019 - (jan 2020 - des 2022)</t>
   </si>
   <si>
@@ -1614,6 +1620,9 @@
   </si>
   <si>
     <t>2019 - (mar 2023 - feb 2026)</t>
+  </si>
+  <si>
+    <t>2019 - (apr 2023 - mar 2026)</t>
   </si>
 </sst>
 </file>
@@ -2148,7 +2157,7 @@
         <v>1.156292824755067</v>
       </c>
       <c r="AD2">
-        <v>0.25458523348818041</v>
+        <v>1.560876367899344</v>
       </c>
       <c r="AE2" t="s">
         <v>42</v>
@@ -2237,7 +2246,7 @@
         <v>0.43</v>
       </c>
       <c r="AD3">
-        <v>-0.57999999999999996</v>
+        <v>-3.06</v>
       </c>
       <c r="AE3" t="s">
         <v>42</v>
@@ -2310,6 +2319,9 @@
       <c r="Y4">
         <v>3.79</v>
       </c>
+      <c r="AD4">
+        <v>4.07</v>
+      </c>
       <c r="AE4" t="s">
         <v>42</v>
       </c>
@@ -2403,7 +2415,7 @@
         <v>-6.53</v>
       </c>
       <c r="AD5">
-        <v>-6.43</v>
+        <v>-6.23</v>
       </c>
       <c r="AE5" t="s">
         <v>42</v>
@@ -2498,7 +2510,7 @@
         <v>-6.72</v>
       </c>
       <c r="AD6">
-        <v>-12.31</v>
+        <v>-10.38</v>
       </c>
       <c r="AE6" t="s">
         <v>42</v>
@@ -2587,7 +2599,7 @@
         <v>7.66</v>
       </c>
       <c r="AD7">
-        <v>6.68</v>
+        <v>7.45</v>
       </c>
       <c r="AE7" t="s">
         <v>42</v>
@@ -2667,7 +2679,7 @@
         <v>0.16591159247651979</v>
       </c>
       <c r="AD8">
-        <v>-2.2133346720438212</v>
+        <v>-2.7000249292074452</v>
       </c>
       <c r="AE8" t="s">
         <v>42</v>
@@ -2753,7 +2765,7 @@
         <v>0.71</v>
       </c>
       <c r="AD9">
-        <v>10.73</v>
+        <v>12.42</v>
       </c>
       <c r="AE9" t="s">
         <v>42</v>
@@ -2842,7 +2854,7 @@
         <v>2.06</v>
       </c>
       <c r="AD10">
-        <v>1.1499999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="AE10" t="s">
         <v>42</v>
@@ -2919,7 +2931,7 @@
         <v>1.452655144252613</v>
       </c>
       <c r="AD11">
-        <v>1.9739135707031561</v>
+        <v>0.94965635418304828</v>
       </c>
       <c r="AE11" t="s">
         <v>93</v>
@@ -2999,7 +3011,7 @@
         <v>15.84</v>
       </c>
       <c r="AD12">
-        <v>8.15</v>
+        <v>7.03</v>
       </c>
       <c r="AE12" t="s">
         <v>93</v>
@@ -3171,7 +3183,7 @@
         <v>-1.61</v>
       </c>
       <c r="AD14">
-        <v>-1.03</v>
+        <v>-1.48</v>
       </c>
       <c r="AE14" t="s">
         <v>93</v>
@@ -3331,7 +3343,7 @@
         <v>-0.38</v>
       </c>
       <c r="AD16">
-        <v>-7.72</v>
+        <v>-8.26</v>
       </c>
       <c r="AE16" t="s">
         <v>93</v>
@@ -3420,7 +3432,7 @@
         <v>-1.22</v>
       </c>
       <c r="AD17">
-        <v>-5.57</v>
+        <v>-6.67</v>
       </c>
       <c r="AE17" t="s">
         <v>93</v>
@@ -3506,7 +3518,7 @@
         <v>-5.6467060046133888</v>
       </c>
       <c r="AD18">
-        <v>-3.940482465510986</v>
+        <v>-3.879939536652544</v>
       </c>
       <c r="AE18" t="s">
         <v>93</v>
@@ -3592,7 +3604,7 @@
         <v>2.8365314882771391</v>
       </c>
       <c r="AD19">
-        <v>2.508889993062025</v>
+        <v>4.5999409869925456</v>
       </c>
       <c r="AE19" t="s">
         <v>131</v>
@@ -3678,7 +3690,7 @@
         <v>2.395929509145867</v>
       </c>
       <c r="AD20">
-        <v>3.1130691125635712</v>
+        <v>3.953712229011463</v>
       </c>
       <c r="AE20" t="s">
         <v>131</v>
@@ -3764,7 +3776,7 @@
         <v>2.14828118146615</v>
       </c>
       <c r="AD21">
-        <v>3.9890239316603182</v>
+        <v>5.9189271070140936</v>
       </c>
       <c r="AE21" t="s">
         <v>131</v>
@@ -3850,7 +3862,7 @@
         <v>16.200949710845119</v>
       </c>
       <c r="AD22">
-        <v>5.5975068920052662</v>
+        <v>7.7784740717530942</v>
       </c>
       <c r="AE22" t="s">
         <v>131</v>
@@ -3936,7 +3948,7 @@
         <v>-31.02</v>
       </c>
       <c r="AD23">
-        <v>-30.44</v>
+        <v>-29.8</v>
       </c>
       <c r="AE23" t="s">
         <v>131</v>
@@ -4087,7 +4099,7 @@
         <v>-5.7793794118043973</v>
       </c>
       <c r="AD25">
-        <v>-11.32947952025831</v>
+        <v>-11.067338109942551</v>
       </c>
       <c r="AE25" t="s">
         <v>131</v>
@@ -4164,7 +4176,7 @@
         <v>3.21</v>
       </c>
       <c r="AD26">
-        <v>0.39</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AE26" t="s">
         <v>131</v>
@@ -4250,7 +4262,7 @@
         <v>15.37018804324128</v>
       </c>
       <c r="AD27">
-        <v>3.9719742027319871</v>
+        <v>2.950597071830074</v>
       </c>
       <c r="AE27" t="s">
         <v>131</v>
@@ -4336,7 +4348,7 @@
         <v>2.976738896294107</v>
       </c>
       <c r="AD28">
-        <v>2.4789332153547279</v>
+        <v>3.0421335359070989</v>
       </c>
       <c r="AE28" t="s">
         <v>131</v>
@@ -4422,7 +4434,7 @@
         <v>-1.19</v>
       </c>
       <c r="AD29">
-        <v>-2.15</v>
+        <v>-0.89</v>
       </c>
       <c r="AE29" t="s">
         <v>131</v>
@@ -4567,7 +4579,7 @@
         <v>4.33</v>
       </c>
       <c r="AD31">
-        <v>-0.28000000000000003</v>
+        <v>-0.85</v>
       </c>
       <c r="AE31" t="s">
         <v>131</v>
@@ -4798,7 +4810,7 @@
         <v>10.048652079471809</v>
       </c>
       <c r="AD34">
-        <v>3.154374243574765</v>
+        <v>4.2057012762951604</v>
       </c>
       <c r="AE34" t="s">
         <v>131</v>
@@ -4884,7 +4896,7 @@
         <v>-1.579566505985031</v>
       </c>
       <c r="AD35">
-        <v>-3.865454697775728</v>
+        <v>-2.7535328726699499</v>
       </c>
       <c r="AE35" t="s">
         <v>131</v>
@@ -4970,7 +4982,7 @@
         <v>-4.8560489755690721</v>
       </c>
       <c r="AD36">
-        <v>-3.046281519310567</v>
+        <v>-2.5007913896802791</v>
       </c>
       <c r="AE36" t="s">
         <v>131</v>
@@ -5050,7 +5062,7 @@
         <v>-3.22</v>
       </c>
       <c r="AD37">
-        <v>2.62</v>
+        <v>3.81</v>
       </c>
       <c r="AE37" t="s">
         <v>131</v>
@@ -5124,7 +5136,7 @@
         <v>0.24</v>
       </c>
       <c r="AD38">
-        <v>1.88</v>
+        <v>4.09</v>
       </c>
       <c r="AE38" t="s">
         <v>131</v>
@@ -5207,7 +5219,7 @@
         <v>-4.6900000000000004</v>
       </c>
       <c r="AD39">
-        <v>-3.73</v>
+        <v>-4.68</v>
       </c>
       <c r="AE39" t="s">
         <v>131</v>
@@ -5287,7 +5299,7 @@
         <v>-4.37</v>
       </c>
       <c r="AD40">
-        <v>-5.0999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="AE40" t="s">
         <v>131</v>
@@ -5373,7 +5385,7 @@
         <v>-4.0184209892491722</v>
       </c>
       <c r="AD41">
-        <v>-0.97014769412656632</v>
+        <v>0.14157676851269671</v>
       </c>
       <c r="AE41" t="s">
         <v>131</v>
@@ -5767,7 +5779,7 @@
         <v>-6.4988907983568822</v>
       </c>
       <c r="AD46">
-        <v>-2.698855439068959</v>
+        <v>-0.61673512322180102</v>
       </c>
       <c r="AE46" t="s">
         <v>283</v>
@@ -5853,7 +5865,7 @@
         <v>-2.948199938752361</v>
       </c>
       <c r="AD47">
-        <v>-1.2624099455280311</v>
+        <v>-1.5243704861136129</v>
       </c>
       <c r="AE47" t="s">
         <v>283</v>
@@ -6019,7 +6031,7 @@
         <v>4.6044313585348773</v>
       </c>
       <c r="AD49">
-        <v>6.6775287486704693</v>
+        <v>7.0690406164354513</v>
       </c>
       <c r="AE49" t="s">
         <v>283</v>
@@ -6105,7 +6117,7 @@
         <v>17.215048582884581</v>
       </c>
       <c r="AD50">
-        <v>24.484491961965229</v>
+        <v>25.052118936603641</v>
       </c>
       <c r="AE50" t="s">
         <v>283</v>
@@ -6191,7 +6203,7 @@
         <v>2.759627515679397</v>
       </c>
       <c r="AD51">
-        <v>2.3835770580136422</v>
+        <v>3.942065053738264</v>
       </c>
       <c r="AE51" t="s">
         <v>283</v>
@@ -6468,6 +6480,9 @@
       <c r="F8">
         <v>-2.1</v>
       </c>
+      <c r="G8">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -6788,6 +6803,9 @@
       <c r="F15">
         <v>-6.2332194460236066</v>
       </c>
+      <c r="G15">
+        <v>-0.62988346355903335</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -7137,6 +7155,9 @@
       <c r="F29">
         <v>-4.3</v>
       </c>
+      <c r="G29">
+        <v>-1.88</v>
+      </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -7457,6 +7478,9 @@
       <c r="F36">
         <v>-16.66461368664298</v>
       </c>
+      <c r="G36">
+        <v>-10.448632083130381</v>
+      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -7762,6 +7786,9 @@
       <c r="F43">
         <v>1.6856210410172161</v>
       </c>
+      <c r="G43">
+        <v>0.57907213003725033</v>
+      </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -8082,6 +8109,9 @@
       <c r="F50">
         <v>4.0508626793189784</v>
       </c>
+      <c r="G50">
+        <v>8.867775508582687</v>
+      </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -8402,6 +8432,9 @@
       <c r="F57">
         <v>-5.3327607470049276</v>
       </c>
+      <c r="G57">
+        <v>-2.0231697371447699</v>
+      </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -8722,6 +8755,9 @@
       <c r="F64">
         <v>-8.25</v>
       </c>
+      <c r="G64">
+        <v>-5.86</v>
+      </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -9042,6 +9078,9 @@
       <c r="F71">
         <v>-15.09</v>
       </c>
+      <c r="G71">
+        <v>-6.95</v>
+      </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -9362,6 +9401,9 @@
       <c r="F78">
         <v>5.17</v>
       </c>
+      <c r="G78">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -9861,6 +9903,9 @@
       <c r="F92">
         <v>-0.84466213514594601</v>
       </c>
+      <c r="G92">
+        <v>6.1895877602020644</v>
+      </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -10145,6 +10190,9 @@
       <c r="F99">
         <v>-4.4000000000000004</v>
       </c>
+      <c r="G99">
+        <v>-2.31</v>
+      </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
@@ -10345,6 +10393,9 @@
       <c r="F106">
         <v>-0.71</v>
       </c>
+      <c r="G106">
+        <v>6.28</v>
+      </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -10566,6 +10617,9 @@
       <c r="E113">
         <v>-3.73</v>
       </c>
+      <c r="G113">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
@@ -11650,6 +11704,9 @@
       <c r="F148">
         <v>-4.34</v>
       </c>
+      <c r="G148">
+        <v>1.55</v>
+      </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
@@ -11970,6 +12027,9 @@
       <c r="F155">
         <v>-1.276526002251765</v>
       </c>
+      <c r="G155">
+        <v>3.905156479061755</v>
+      </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -12290,6 +12350,9 @@
       <c r="F162">
         <v>0.40232011204186507</v>
       </c>
+      <c r="G162">
+        <v>5.4316897628433392</v>
+      </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
@@ -12610,6 +12673,9 @@
       <c r="F169">
         <v>-0.34413195680550462</v>
       </c>
+      <c r="G169">
+        <v>11.8923807370563</v>
+      </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
@@ -12924,6 +12990,9 @@
       <c r="F176">
         <v>-3.2854283716331918</v>
       </c>
+      <c r="G176">
+        <v>2.2478964858940742</v>
+      </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
@@ -13199,6 +13268,9 @@
       <c r="F183">
         <v>-3.78</v>
       </c>
+      <c r="G183">
+        <v>-8.11</v>
+      </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
@@ -13519,6 +13591,9 @@
       <c r="F190">
         <v>2.1261861081074418</v>
       </c>
+      <c r="G190">
+        <v>7.8095482231522304</v>
+      </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -14069,6 +14144,9 @@
       <c r="F204">
         <v>2.39</v>
       </c>
+      <c r="G204">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
@@ -14389,6 +14467,9 @@
       <c r="F211">
         <v>-2.9432139817508811</v>
       </c>
+      <c r="G211">
+        <v>3.2668364967170178</v>
+      </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
@@ -14783,6 +14864,9 @@
       <c r="F225">
         <v>1.7245832257204441</v>
       </c>
+      <c r="G225">
+        <v>-1.477786060045438</v>
+      </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
@@ -14977,6 +15061,9 @@
       <c r="F232">
         <v>6.36</v>
       </c>
+      <c r="G232">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
@@ -15123,6 +15210,9 @@
       <c r="F239">
         <v>-5.0999999999999996</v>
       </c>
+      <c r="G239">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
@@ -15437,6 +15527,9 @@
       <c r="F246">
         <v>-3.7559276889436828</v>
       </c>
+      <c r="G246">
+        <v>-3.5527617171160371</v>
+      </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
@@ -15757,6 +15850,9 @@
       <c r="F253">
         <v>-6.2244531657712372</v>
       </c>
+      <c r="G253">
+        <v>-3.7677402737609</v>
+      </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
@@ -16059,6 +16155,9 @@
       <c r="F260">
         <v>-9.51</v>
       </c>
+      <c r="G260">
+        <v>-8.67</v>
+      </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
@@ -16361,6 +16460,9 @@
       <c r="F267">
         <v>-11.55</v>
       </c>
+      <c r="G267">
+        <v>-9.25</v>
+      </c>
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
@@ -16474,6 +16576,9 @@
       <c r="D274">
         <v>2026</v>
       </c>
+      <c r="G274">
+        <v>4.07</v>
+      </c>
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
@@ -16719,6 +16824,9 @@
       <c r="F281">
         <v>-32.33</v>
       </c>
+      <c r="G281">
+        <v>-28.59</v>
+      </c>
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
@@ -17039,6 +17147,9 @@
       <c r="F288">
         <v>21.525114729364429</v>
       </c>
+      <c r="G288">
+        <v>26.13263814827982</v>
+      </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
@@ -17359,6 +17470,9 @@
       <c r="F295">
         <v>-0.19839374132378801</v>
       </c>
+      <c r="G295">
+        <v>4.1071965487940343</v>
+      </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
@@ -17661,6 +17775,9 @@
       <c r="F302">
         <v>-6.3702261724853386</v>
       </c>
+      <c r="G302">
+        <v>-1.5487120064176849</v>
+      </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
@@ -17981,6 +18098,9 @@
       <c r="F309">
         <v>0.23586346230648481</v>
       </c>
+      <c r="G309">
+        <v>6.9713579522469482</v>
+      </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
@@ -18301,6 +18421,9 @@
       <c r="F316">
         <v>0.14306923040976471</v>
       </c>
+      <c r="G316">
+        <v>9.533269109391096</v>
+      </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
@@ -18450,6 +18573,9 @@
       <c r="F323">
         <v>1.92</v>
       </c>
+      <c r="G323">
+        <v>8.35</v>
+      </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
@@ -18769,6 +18895,9 @@
       </c>
       <c r="F330">
         <v>-0.77</v>
+      </c>
+      <c r="G330">
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>
@@ -19118,16 +19247,16 @@
         <v>2026</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>-0.51240514139074822</v>
+        <v>-0.18486935601419449</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>1.359545195823963</v>
+        <v>1.343777926810759</v>
       </c>
       <c r="G8">
         <v>2025</v>
@@ -19136,7 +19265,7 @@
         <v>354</v>
       </c>
       <c r="I8">
-        <v>0.99487594858609252</v>
+        <v>0.99815130643985805</v>
       </c>
       <c r="J8" t="s">
         <v>347</v>
@@ -19145,16 +19274,16 @@
         <v>37</v>
       </c>
       <c r="L8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M8" t="s">
         <v>355</v>
       </c>
       <c r="N8">
-        <v>-3.2</v>
+        <v>-2.8</v>
       </c>
       <c r="O8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -19460,7 +19589,7 @@
         <v>2020</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>345</v>
@@ -19469,16 +19598,16 @@
         <v>38</v>
       </c>
       <c r="F2">
-        <v>8.2511545859854696</v>
+        <v>7.7149788067621463</v>
       </c>
       <c r="G2">
-        <v>1.711124906335167</v>
+        <v>1.5997119438781171</v>
       </c>
       <c r="H2">
-        <v>1.0290941354882079</v>
+        <v>0.93259747300451301</v>
       </c>
       <c r="I2">
-        <v>2.9094135488208379</v>
+        <v>-6.7402526995486989</v>
       </c>
       <c r="K2" t="s">
         <v>346</v>
@@ -19487,7 +19616,7 @@
         <v>37</v>
       </c>
       <c r="M2" s="2">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="N2" t="s">
         <v>365</v>
@@ -19504,7 +19633,7 @@
         <v>2021</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>345</v>
@@ -19513,16 +19642,16 @@
         <v>42</v>
       </c>
       <c r="F3">
-        <v>7.6110023735964063</v>
+        <v>7.606726065129565</v>
       </c>
       <c r="G3">
-        <v>1.53704017267703</v>
+        <v>1.554258284967198</v>
       </c>
       <c r="H3">
-        <v>0.83817281882034489</v>
+        <v>0.94924892467713895</v>
       </c>
       <c r="I3">
-        <v>-16.182718117965511</v>
+        <v>-5.075107532286105</v>
       </c>
       <c r="K3" t="s">
         <v>349</v>
@@ -19531,7 +19660,7 @@
         <v>37</v>
       </c>
       <c r="M3" s="2">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="N3" t="s">
         <v>365</v>
@@ -19548,25 +19677,25 @@
         <v>2022</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>345</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>18.12657011917365</v>
+        <v>17.35439970337195</v>
       </c>
       <c r="G4">
-        <v>3.600669622858379</v>
+        <v>3.4566572444489778</v>
       </c>
       <c r="H4">
-        <v>1.095847375709049</v>
+        <v>1.1126209694585949</v>
       </c>
       <c r="I4">
-        <v>9.5847375709049221</v>
+        <v>11.26209694585947</v>
       </c>
       <c r="K4" t="s">
         <v>350</v>
@@ -19575,7 +19704,7 @@
         <v>37</v>
       </c>
       <c r="M4" s="2">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="N4" t="s">
         <v>365</v>
@@ -19592,7 +19721,7 @@
         <v>2023</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
         <v>345</v>
@@ -19601,16 +19730,16 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>6.8947316767572264</v>
+        <v>5.4999966531252298</v>
       </c>
       <c r="G5">
-        <v>1.384870819919312</v>
+        <v>1.1183241017602901</v>
       </c>
       <c r="H5">
-        <v>1.0954004391893111</v>
+        <v>1.0527315893395051</v>
       </c>
       <c r="I5">
-        <v>9.5400439189311079</v>
+        <v>5.2731589339504836</v>
       </c>
       <c r="K5" t="s">
         <v>351</v>
@@ -19619,7 +19748,7 @@
         <v>37</v>
       </c>
       <c r="M5" s="2">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="N5" t="s">
         <v>365</v>
@@ -19636,7 +19765,7 @@
         <v>2024</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>345</v>
@@ -19645,16 +19774,16 @@
         <v>34</v>
       </c>
       <c r="F6">
-        <v>12.937038622847369</v>
+        <v>12.7999507769056</v>
       </c>
       <c r="G6">
-        <v>2.7071561217834139</v>
+        <v>2.680336137611655</v>
       </c>
       <c r="H6">
-        <v>0.98335245448497921</v>
+        <v>0.95289283071302733</v>
       </c>
       <c r="I6">
-        <v>-1.664754551502079</v>
+        <v>-4.7107169286972672</v>
       </c>
       <c r="K6" t="s">
         <v>352</v>
@@ -19663,7 +19792,7 @@
         <v>37</v>
       </c>
       <c r="M6" s="2">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="N6" t="s">
         <v>365</v>
@@ -19680,7 +19809,7 @@
         <v>2025</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>345</v>
@@ -19689,16 +19818,16 @@
         <v>35</v>
       </c>
       <c r="F7">
-        <v>4.9781444699419994</v>
+        <v>5.32378278556636</v>
       </c>
       <c r="G7">
-        <v>1.0795727727903419</v>
+        <v>1.157245324091331</v>
       </c>
       <c r="H7">
-        <v>1.014615574323785</v>
+        <v>1.0364130121101389</v>
       </c>
       <c r="I7">
-        <v>1.461557432378457</v>
+        <v>3.641301211013936</v>
       </c>
       <c r="K7" t="s">
         <v>353</v>
@@ -19707,7 +19836,7 @@
         <v>37</v>
       </c>
       <c r="M7" s="2">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="N7" t="s">
         <v>365</v>
@@ -19724,25 +19853,25 @@
         <v>2026</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>345</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>6.5659251799349203</v>
+        <v>6.6618124189277594</v>
       </c>
       <c r="G8">
-        <v>1.3596166263529741</v>
+        <v>1.343713716388931</v>
       </c>
       <c r="H8">
-        <v>0.99487594858609252</v>
+        <v>0.99815130643985805</v>
       </c>
       <c r="I8">
-        <v>-0.51240514139074822</v>
+        <v>-0.18486935601419449</v>
       </c>
       <c r="K8" t="s">
         <v>354</v>
@@ -19751,7 +19880,7 @@
         <v>37</v>
       </c>
       <c r="M8" s="2">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="N8" t="s">
         <v>365</v>
@@ -19768,7 +19897,7 @@
         <v>2021</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>345</v>
@@ -19777,13 +19906,13 @@
         <v>42</v>
       </c>
       <c r="G9">
-        <v>2.1353303553284548</v>
+        <v>2.099423364484263</v>
       </c>
       <c r="H9">
-        <v>0.86255873237363756</v>
+        <v>0.88526714840615106</v>
       </c>
       <c r="I9">
-        <v>-13.74412676263624</v>
+        <v>-11.47328515938489</v>
       </c>
       <c r="J9" t="s">
         <v>357</v>
@@ -19795,7 +19924,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="2">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="N9" t="s">
         <v>365</v>
@@ -19812,7 +19941,7 @@
         <v>2022</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
         <v>345</v>
@@ -19821,13 +19950,13 @@
         <v>42</v>
       </c>
       <c r="G10">
-        <v>3.8893982845090238</v>
+        <v>3.850391959416922</v>
       </c>
       <c r="H10">
-        <v>0.94523272326657481</v>
+        <v>0.9849667928894974</v>
       </c>
       <c r="I10">
-        <v>-5.4767276733425181</v>
+        <v>-1.50332071105026</v>
       </c>
       <c r="J10" t="s">
         <v>357</v>
@@ -19839,7 +19968,7 @@
         <v>37</v>
       </c>
       <c r="M10" s="2">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="N10" t="s">
         <v>365</v>
@@ -19856,7 +19985,7 @@
         <v>2023</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
         <v>345</v>
@@ -19865,13 +19994,13 @@
         <v>42</v>
       </c>
       <c r="G11">
-        <v>4.4573389410326199</v>
+        <v>4.2006513456027363</v>
       </c>
       <c r="H11">
-        <v>1.0354083402023151</v>
+        <v>1.036905657325196</v>
       </c>
       <c r="I11">
-        <v>3.5408340202314652</v>
+        <v>3.6905657325195569</v>
       </c>
       <c r="J11" t="s">
         <v>357</v>
@@ -19883,7 +20012,7 @@
         <v>37</v>
       </c>
       <c r="M11" s="2">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="N11" t="s">
         <v>365</v>
@@ -19900,7 +20029,7 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>345</v>
@@ -19909,13 +20038,13 @@
         <v>42</v>
       </c>
       <c r="G12">
-        <v>5.2041628581601174</v>
+        <v>4.8743318745265878</v>
       </c>
       <c r="H12">
-        <v>1.018171332732164</v>
+        <v>0.98805996699095788</v>
       </c>
       <c r="I12">
-        <v>1.817133273216442</v>
+        <v>-1.1940033009042119</v>
       </c>
       <c r="J12" t="s">
         <v>357</v>
@@ -19927,7 +20056,7 @@
         <v>37</v>
       </c>
       <c r="M12" s="2">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="N12" t="s">
         <v>365</v>
@@ -19944,7 +20073,7 @@
         <v>2025</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>345</v>
@@ -19953,13 +20082,13 @@
         <v>42</v>
       </c>
       <c r="G13">
-        <v>5.3937137493106846</v>
+        <v>5.1799135278045094</v>
       </c>
       <c r="H13">
-        <v>1.0330524915200581</v>
+        <v>1.024038206534543</v>
       </c>
       <c r="I13">
-        <v>3.3052491520058069</v>
+        <v>2.4038206534543471</v>
       </c>
       <c r="J13" t="s">
         <v>357</v>
@@ -19971,7 +20100,7 @@
         <v>37</v>
       </c>
       <c r="M13" s="2">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="N13" t="s">
         <v>365</v>
@@ -19988,7 +20117,7 @@
         <v>2026</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>345</v>
@@ -19997,13 +20126,13 @@
         <v>42</v>
       </c>
       <c r="G14">
-        <v>5.5473350438633124</v>
+        <v>5.350761538384619</v>
       </c>
       <c r="H14">
-        <v>1.0277590774402441</v>
+        <v>1.0221450736967841</v>
       </c>
       <c r="I14">
-        <v>2.775907744024408</v>
+        <v>2.214507369678365</v>
       </c>
       <c r="J14" t="s">
         <v>357</v>
@@ -20015,7 +20144,7 @@
         <v>37</v>
       </c>
       <c r="M14" s="2">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="N14" t="s">
         <v>365</v>
@@ -20031,7 +20160,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -22581,10 +22710,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>1.0380231758410481</v>
+        <v>1.038057740549178</v>
       </c>
       <c r="B63">
-        <v>3.8023175841047641</v>
+        <v>3.8057740549178209</v>
       </c>
       <c r="C63">
         <v>30</v>
@@ -22593,10 +22722,10 @@
         <v>18.168561844655869</v>
       </c>
       <c r="E63">
-        <v>14.049893446235179</v>
+        <v>14.04133389678509</v>
       </c>
       <c r="F63">
-        <v>3.2961939264048512</v>
+        <v>3.2941858019291672</v>
       </c>
       <c r="G63">
         <v>-2.9</v>
@@ -22622,28 +22751,28 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>1.043082497320406</v>
+        <v>1.0351607011083399</v>
       </c>
       <c r="B64">
-        <v>4.3082497320406032</v>
+        <v>3.5160701108340349</v>
       </c>
       <c r="C64">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D64">
-        <v>17.502576058816331</v>
+        <v>18.168561844655869</v>
       </c>
       <c r="E64">
-        <v>13.56975992209458</v>
+        <v>14.393158469208821</v>
       </c>
       <c r="F64">
-        <v>3.2435543338725381</v>
+        <v>3.3767260733711431</v>
       </c>
       <c r="G64">
-        <v>-2.2999999999999998</v>
+        <v>-3.4</v>
       </c>
       <c r="H64">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="I64" t="s">
         <v>437</v>
@@ -22663,51 +22792,51 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.96207169594373643</v>
+        <v>1.026887099279278</v>
       </c>
       <c r="B65">
-        <v>-3.7928304056263569</v>
+        <v>2.6887099279277571</v>
       </c>
       <c r="C65">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D65">
-        <v>19.337424422271599</v>
+        <v>19.165717644383609</v>
       </c>
       <c r="E65">
-        <v>6.5729663936765563</v>
+        <v>14.884056689115591</v>
       </c>
       <c r="F65">
-        <v>1.4947277492212481</v>
+        <v>3.3998422971460229</v>
       </c>
       <c r="G65">
-        <v>-6.8</v>
+        <v>-4.3</v>
       </c>
       <c r="H65">
-        <v>-0.7</v>
+        <v>9.6</v>
       </c>
       <c r="I65" t="s">
         <v>438</v>
       </c>
       <c r="J65" s="2">
-        <v>44531</v>
+        <v>46082</v>
       </c>
       <c r="K65">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="M65" t="s">
-        <v>439</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>0.9584767458792669</v>
+        <v>0.96207169594373643</v>
       </c>
       <c r="B66">
-        <v>-4.15232541207331</v>
+        <v>-3.7928304056263569</v>
       </c>
       <c r="C66">
         <v>33</v>
@@ -22716,39 +22845,39 @@
         <v>19.337424422271599</v>
       </c>
       <c r="E66">
-        <v>6.8564242911102804</v>
+        <v>6.5729663936765563</v>
       </c>
       <c r="F66">
-        <v>1.5591875927156109</v>
+        <v>1.4947277492212481</v>
       </c>
       <c r="G66">
-        <v>-7.3</v>
+        <v>-6.8</v>
       </c>
       <c r="H66">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="I66" t="s">
+        <v>439</v>
+      </c>
+      <c r="J66" s="2">
+        <v>44531</v>
+      </c>
+      <c r="K66">
+        <v>12</v>
+      </c>
+      <c r="L66">
+        <v>2021</v>
+      </c>
+      <c r="M66" t="s">
         <v>440</v>
-      </c>
-      <c r="J66" s="2">
-        <v>44562</v>
-      </c>
-      <c r="K66">
-        <v>1</v>
-      </c>
-      <c r="L66">
-        <v>2022</v>
-      </c>
-      <c r="M66" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>0.95623467305970444</v>
+        <v>0.9584767458792669</v>
       </c>
       <c r="B67">
-        <v>-4.3765326940295557</v>
+        <v>-4.15232541207331</v>
       </c>
       <c r="C67">
         <v>33</v>
@@ -22757,39 +22886,39 @@
         <v>19.337424422271599</v>
       </c>
       <c r="E67">
-        <v>7.1080610637743114</v>
+        <v>6.8564242911102804</v>
       </c>
       <c r="F67">
-        <v>1.6164111420688001</v>
+        <v>1.5591875927156109</v>
       </c>
       <c r="G67">
-        <v>-7.7</v>
+        <v>-7.3</v>
       </c>
       <c r="H67">
-        <v>-1.1000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="I67" t="s">
         <v>441</v>
       </c>
       <c r="J67" s="2">
-        <v>44593</v>
+        <v>44562</v>
       </c>
       <c r="K67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67">
         <v>2022</v>
       </c>
       <c r="M67" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.96967098630041737</v>
+        <v>0.95623467305970444</v>
       </c>
       <c r="B68">
-        <v>-3.032901369958263</v>
+        <v>-4.3765326940295557</v>
       </c>
       <c r="C68">
         <v>33</v>
@@ -22798,80 +22927,80 @@
         <v>19.337424422271599</v>
       </c>
       <c r="E68">
-        <v>7.2946243969252933</v>
+        <v>7.1080610637743114</v>
       </c>
       <c r="F68">
-        <v>1.65883664287712</v>
+        <v>1.6164111420688001</v>
       </c>
       <c r="G68">
-        <v>-6.4</v>
+        <v>-7.7</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="I68" t="s">
         <v>442</v>
       </c>
       <c r="J68" s="2">
-        <v>44621</v>
+        <v>44593</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L68">
         <v>2022</v>
       </c>
       <c r="M68" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>0.98314960505714111</v>
+        <v>0.96967098630041737</v>
       </c>
       <c r="B69">
-        <v>-1.6850394942858891</v>
+        <v>-3.032901369958263</v>
       </c>
       <c r="C69">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D69">
-        <v>18.99572897372909</v>
+        <v>19.337424422271599</v>
       </c>
       <c r="E69">
-        <v>7.3452258637017636</v>
+        <v>7.2946243969252933</v>
       </c>
       <c r="F69">
-        <v>1.6852998126063909</v>
+        <v>1.65883664287712</v>
       </c>
       <c r="G69">
-        <v>-5.0999999999999996</v>
+        <v>-6.4</v>
       </c>
       <c r="H69">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="I69" t="s">
         <v>443</v>
       </c>
       <c r="J69" s="2">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L69">
         <v>2022</v>
       </c>
       <c r="M69" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>0.99211704434259562</v>
+        <v>0.98314960505714111</v>
       </c>
       <c r="B70">
-        <v>-0.7882955657404378</v>
+        <v>-1.6850394942858891</v>
       </c>
       <c r="C70">
         <v>32</v>
@@ -22880,39 +23009,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E70">
-        <v>7.7307868893566791</v>
+        <v>7.3452258637017636</v>
       </c>
       <c r="F70">
-        <v>1.773763521734198</v>
+        <v>1.6852998126063909</v>
       </c>
       <c r="G70">
-        <v>-4.4000000000000004</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="H70">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="I70" t="s">
         <v>444</v>
       </c>
       <c r="J70" s="2">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L70">
         <v>2022</v>
       </c>
       <c r="M70" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>0.99492372613563573</v>
+        <v>0.99211704434259562</v>
       </c>
       <c r="B71">
-        <v>-0.50762738643642669</v>
+        <v>-0.7882955657404378</v>
       </c>
       <c r="C71">
         <v>32</v>
@@ -22921,39 +23050,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E71">
-        <v>8.2498287820012379</v>
+        <v>7.7307868893566791</v>
       </c>
       <c r="F71">
-        <v>1.8928532843419741</v>
+        <v>1.773763521734198</v>
       </c>
       <c r="G71">
         <v>-4.4000000000000004</v>
       </c>
       <c r="H71">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="I71" t="s">
         <v>445</v>
       </c>
       <c r="J71" s="2">
-        <v>44713</v>
+        <v>44682</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
         <v>2022</v>
       </c>
       <c r="M71" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>0.99264866394161277</v>
+        <v>0.99492372613563573</v>
       </c>
       <c r="B72">
-        <v>-0.73513360583872256</v>
+        <v>-0.50762738643642669</v>
       </c>
       <c r="C72">
         <v>32</v>
@@ -22962,39 +23091,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E72">
-        <v>8.696961507495244</v>
+        <v>8.2498287820012379</v>
       </c>
       <c r="F72">
-        <v>1.9954440980852379</v>
+        <v>1.8928532843419741</v>
       </c>
       <c r="G72">
-        <v>-4.8</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="H72">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I72" t="s">
         <v>446</v>
       </c>
       <c r="J72" s="2">
-        <v>44743</v>
+        <v>44713</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72">
         <v>2022</v>
       </c>
       <c r="M72" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>0.99622510648929574</v>
+        <v>0.99264866394161277</v>
       </c>
       <c r="B73">
-        <v>-0.3774893510704258</v>
+        <v>-0.73513360583872256</v>
       </c>
       <c r="C73">
         <v>32</v>
@@ -23003,39 +23132,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E73">
-        <v>9.0620825329680272</v>
+        <v>8.696961507495244</v>
       </c>
       <c r="F73">
-        <v>2.0792180224309531</v>
+        <v>1.9954440980852379</v>
       </c>
       <c r="G73">
-        <v>-4.5999999999999996</v>
+        <v>-4.8</v>
       </c>
       <c r="H73">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="I73" t="s">
         <v>447</v>
       </c>
       <c r="J73" s="2">
-        <v>44774</v>
+        <v>44743</v>
       </c>
       <c r="K73">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L73">
         <v>2022</v>
       </c>
       <c r="M73" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>0.9975049879886283</v>
+        <v>0.99622510648929574</v>
       </c>
       <c r="B74">
-        <v>-0.24950120113717</v>
+        <v>-0.3774893510704258</v>
       </c>
       <c r="C74">
         <v>32</v>
@@ -23044,39 +23173,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E74">
-        <v>9.4662779911143087</v>
+        <v>9.0620825329680272</v>
       </c>
       <c r="F74">
-        <v>2.171957244139104</v>
+        <v>2.0792180224309531</v>
       </c>
       <c r="G74">
-        <v>-4.7</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="H74">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I74" t="s">
         <v>448</v>
       </c>
       <c r="J74" s="2">
-        <v>44805</v>
+        <v>44774</v>
       </c>
       <c r="K74">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L74">
         <v>2022</v>
       </c>
       <c r="M74" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>0.99780749849508021</v>
+        <v>0.9975049879886283</v>
       </c>
       <c r="B75">
-        <v>-0.2192501504919786</v>
+        <v>-0.24950120113717</v>
       </c>
       <c r="C75">
         <v>32</v>
@@ -23085,39 +23214,39 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E75">
-        <v>9.861193498544198</v>
+        <v>9.4662779911143087</v>
       </c>
       <c r="F75">
-        <v>2.2625672598168971</v>
+        <v>2.171957244139104</v>
       </c>
       <c r="G75">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="H75">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="I75" t="s">
         <v>449</v>
       </c>
       <c r="J75" s="2">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="K75">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L75">
         <v>2022</v>
       </c>
       <c r="M75" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>1.002827544586588</v>
+        <v>0.99780749849508021</v>
       </c>
       <c r="B76">
-        <v>0.28275445865884041</v>
+        <v>-0.2192501504919786</v>
       </c>
       <c r="C76">
         <v>32</v>
@@ -23126,80 +23255,80 @@
         <v>18.99572897372909</v>
       </c>
       <c r="E76">
-        <v>10.29478373440373</v>
+        <v>9.861193498544198</v>
       </c>
       <c r="F76">
-        <v>2.3620508641064668</v>
+        <v>2.2625672598168971</v>
       </c>
       <c r="G76">
-        <v>-4.5</v>
+        <v>-4.8</v>
       </c>
       <c r="H76">
-        <v>5.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I76" t="s">
         <v>450</v>
       </c>
       <c r="J76" s="2">
-        <v>44866</v>
+        <v>44835</v>
       </c>
       <c r="K76">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L76">
         <v>2022</v>
       </c>
       <c r="M76" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>0.99948637435896082</v>
+        <v>1.002827544586588</v>
       </c>
       <c r="B77">
-        <v>-5.1362564103918373E-2</v>
+        <v>0.28275445865884041</v>
       </c>
       <c r="C77">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D77">
-        <v>21.753475225948449</v>
+        <v>18.99572897372909</v>
       </c>
       <c r="E77">
-        <v>11.35275219731734</v>
+        <v>10.29478373440373</v>
       </c>
       <c r="F77">
-        <v>2.434091134743976</v>
+        <v>2.3620508641064668</v>
       </c>
       <c r="G77">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
       <c r="H77">
-        <v>4.9000000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I77" t="s">
         <v>451</v>
       </c>
       <c r="J77" s="2">
-        <v>44896</v>
+        <v>44866</v>
       </c>
       <c r="K77">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L77">
         <v>2022</v>
       </c>
       <c r="M77" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>1.0084092225514021</v>
+        <v>0.99948637435896082</v>
       </c>
       <c r="B78">
-        <v>0.84092225514016405</v>
+        <v>-5.1362564103918373E-2</v>
       </c>
       <c r="C78">
         <v>31</v>
@@ -23208,80 +23337,80 @@
         <v>21.753475225948449</v>
       </c>
       <c r="E78">
-        <v>11.84406842320638</v>
+        <v>11.35275219731734</v>
       </c>
       <c r="F78">
-        <v>2.5394319762427431</v>
+        <v>2.434091134743976</v>
       </c>
       <c r="G78">
-        <v>-4.3</v>
+        <v>-5</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I78" t="s">
         <v>452</v>
       </c>
       <c r="J78" s="2">
-        <v>44927</v>
+        <v>44896</v>
       </c>
       <c r="K78">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L78">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="M78" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>1.015064545218932</v>
+        <v>1.0084092225514021</v>
       </c>
       <c r="B79">
-        <v>1.5064545218931751</v>
+        <v>0.84092225514016405</v>
       </c>
       <c r="C79">
         <v>31</v>
       </c>
       <c r="D79">
-        <v>21.633075473219431</v>
+        <v>21.753475225948449</v>
       </c>
       <c r="E79">
-        <v>12.297003170968541</v>
+        <v>11.84406842320638</v>
       </c>
       <c r="F79">
-        <v>2.6438703371031882</v>
+        <v>2.5394319762427431</v>
       </c>
       <c r="G79">
-        <v>-3.9</v>
+        <v>-4.3</v>
       </c>
       <c r="H79">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="I79" t="s">
         <v>453</v>
       </c>
       <c r="J79" s="2">
-        <v>44958</v>
+        <v>44927</v>
       </c>
       <c r="K79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79">
         <v>2023</v>
       </c>
       <c r="M79" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>1.0199159397341271</v>
+        <v>1.015064545218932</v>
       </c>
       <c r="B80">
-        <v>1.991593973412664</v>
+        <v>1.5064545218931751</v>
       </c>
       <c r="C80">
         <v>31</v>
@@ -23290,39 +23419,39 @@
         <v>21.633075473219431</v>
       </c>
       <c r="E80">
-        <v>12.6993882343256</v>
+        <v>12.297003170968541</v>
       </c>
       <c r="F80">
-        <v>2.7303836052801631</v>
+        <v>2.6438703371031882</v>
       </c>
       <c r="G80">
-        <v>-3.6</v>
+        <v>-3.9</v>
       </c>
       <c r="H80">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="I80" t="s">
         <v>454</v>
       </c>
       <c r="J80" s="2">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L80">
         <v>2023</v>
       </c>
       <c r="M80" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>1.020389170746602</v>
+        <v>1.0199159397341271</v>
       </c>
       <c r="B81">
-        <v>2.038917074660151</v>
+        <v>1.991593973412664</v>
       </c>
       <c r="C81">
         <v>31</v>
@@ -23331,80 +23460,80 @@
         <v>21.633075473219431</v>
       </c>
       <c r="E81">
-        <v>13.010751075673729</v>
+        <v>12.6993882343256</v>
       </c>
       <c r="F81">
-        <v>2.797326987246588</v>
+        <v>2.7303836052801631</v>
       </c>
       <c r="G81">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="H81">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I81" t="s">
         <v>455</v>
       </c>
       <c r="J81" s="2">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="K81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81">
         <v>2023</v>
       </c>
       <c r="M81" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>1.0282985826231039</v>
+        <v>1.020389170746602</v>
       </c>
       <c r="B82">
-        <v>2.8298582623103701</v>
+        <v>2.038917074660151</v>
       </c>
       <c r="C82">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D82">
-        <v>20.93488312862889</v>
+        <v>21.633075473219431</v>
       </c>
       <c r="E82">
-        <v>13.212893890374691</v>
+        <v>13.010751075673729</v>
       </c>
       <c r="F82">
-        <v>2.88777050909819</v>
+        <v>2.797326987246588</v>
       </c>
       <c r="G82">
-        <v>-3.1</v>
+        <v>-3.7</v>
       </c>
       <c r="H82">
-        <v>8.6999999999999993</v>
+        <v>7.8</v>
       </c>
       <c r="I82" t="s">
         <v>456</v>
       </c>
       <c r="J82" s="2">
-        <v>45047</v>
+        <v>45017</v>
       </c>
       <c r="K82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82">
         <v>2023</v>
       </c>
       <c r="M82" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>1.033360016995347</v>
+        <v>1.0282985826231039</v>
       </c>
       <c r="B83">
-        <v>3.336001699534719</v>
+        <v>2.8298582623103701</v>
       </c>
       <c r="C83">
         <v>30</v>
@@ -23413,39 +23542,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E83">
-        <v>13.267231602005291</v>
+        <v>13.212893890374691</v>
       </c>
       <c r="F83">
-        <v>2.8996463965820851</v>
+        <v>2.88777050909819</v>
       </c>
       <c r="G83">
-        <v>-2.6</v>
+        <v>-3.1</v>
       </c>
       <c r="H83">
-        <v>9.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="I83" t="s">
         <v>457</v>
       </c>
       <c r="J83" s="2">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="K83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L83">
         <v>2023</v>
       </c>
       <c r="M83" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>1.031839985059567</v>
+        <v>1.033360016995347</v>
       </c>
       <c r="B84">
-        <v>3.183998505956676</v>
+        <v>3.336001699534719</v>
       </c>
       <c r="C84">
         <v>30</v>
@@ -23454,39 +23583,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E84">
-        <v>13.24170442730207</v>
+        <v>13.267231602005291</v>
       </c>
       <c r="F84">
-        <v>2.894067253746293</v>
+        <v>2.8996463965820851</v>
       </c>
       <c r="G84">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="H84">
-        <v>9.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I84" t="s">
         <v>458</v>
       </c>
       <c r="J84" s="2">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="K84">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L84">
         <v>2023</v>
       </c>
       <c r="M84" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>1.0328935817482541</v>
+        <v>1.031839985059567</v>
       </c>
       <c r="B85">
-        <v>3.2893581748254301</v>
+        <v>3.183998505956676</v>
       </c>
       <c r="C85">
         <v>30</v>
@@ -23495,39 +23624,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E85">
-        <v>13.618023969837679</v>
+        <v>13.24170442730207</v>
       </c>
       <c r="F85">
-        <v>2.976314525687477</v>
+        <v>2.894067253746293</v>
       </c>
       <c r="G85">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="H85">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I85" t="s">
         <v>459</v>
       </c>
       <c r="J85" s="2">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="K85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L85">
         <v>2023</v>
       </c>
       <c r="M85" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>1.0349462292480129</v>
+        <v>1.0328935817482541</v>
       </c>
       <c r="B86">
-        <v>3.4946229248013161</v>
+        <v>3.2893581748254301</v>
       </c>
       <c r="C86">
         <v>30</v>
@@ -23536,39 +23665,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E86">
-        <v>14.12095938059085</v>
+        <v>13.618023969837679</v>
       </c>
       <c r="F86">
-        <v>3.086234582505023</v>
+        <v>2.976314525687477</v>
       </c>
       <c r="G86">
         <v>-2.8</v>
       </c>
       <c r="H86">
-        <v>9.8000000000000007</v>
+        <v>9.4</v>
       </c>
       <c r="I86" t="s">
         <v>460</v>
       </c>
       <c r="J86" s="2">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="K86">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L86">
         <v>2023</v>
       </c>
       <c r="M86" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>1.034597951552986</v>
+        <v>1.0349462292480129</v>
       </c>
       <c r="B87">
-        <v>3.4597951552986168</v>
+        <v>3.4946229248013161</v>
       </c>
       <c r="C87">
         <v>30</v>
@@ -23577,80 +23706,80 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E87">
-        <v>14.547089355302431</v>
+        <v>14.12095938059085</v>
       </c>
       <c r="F87">
-        <v>3.1793682732940858</v>
+        <v>3.086234582505023</v>
       </c>
       <c r="G87">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="H87">
-        <v>10</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I87" t="s">
         <v>461</v>
       </c>
       <c r="J87" s="2">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="K87">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L87">
         <v>2023</v>
       </c>
       <c r="M87" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>1.05360188334448</v>
+        <v>1.034597951552986</v>
       </c>
       <c r="B88">
-        <v>5.3601883344480461</v>
+        <v>3.4597951552986168</v>
       </c>
       <c r="C88">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D88">
-        <v>19.115832380573561</v>
+        <v>20.93488312862889</v>
       </c>
       <c r="E88">
-        <v>10.24802034867216</v>
+        <v>14.547089355302431</v>
       </c>
       <c r="F88">
-        <v>2.343923170642384</v>
+        <v>3.1793682732940858</v>
       </c>
       <c r="G88">
-        <v>0.6</v>
+        <v>-3</v>
       </c>
       <c r="H88">
-        <v>10.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I88" t="s">
         <v>462</v>
       </c>
       <c r="J88" s="2">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="K88">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L88">
         <v>2023</v>
       </c>
       <c r="M88" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>1.0546279856219181</v>
+        <v>1.05360188334448</v>
       </c>
       <c r="B89">
-        <v>5.4627985621918276</v>
+        <v>5.3601883344480461</v>
       </c>
       <c r="C89">
         <v>28</v>
@@ -23659,39 +23788,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E89">
-        <v>10.24493765100048</v>
+        <v>10.24802034867216</v>
       </c>
       <c r="F89">
-        <v>2.3432180972472412</v>
+        <v>2.343923170642384</v>
       </c>
       <c r="G89">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H89">
-        <v>10.3</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I89" t="s">
         <v>463</v>
       </c>
       <c r="J89" s="2">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="K89">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L89">
         <v>2023</v>
       </c>
       <c r="M89" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>1.0583104067237841</v>
+        <v>1.0546279856219181</v>
       </c>
       <c r="B90">
-        <v>5.8310406723783634</v>
+        <v>5.4627985621918276</v>
       </c>
       <c r="C90">
         <v>28</v>
@@ -23700,39 +23829,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E90">
-        <v>10.03569929372812</v>
+        <v>10.24493765100048</v>
       </c>
       <c r="F90">
-        <v>2.295361182729954</v>
+        <v>2.3432180972472412</v>
       </c>
       <c r="G90">
-        <v>1.1000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H90">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="I90" t="s">
         <v>464</v>
       </c>
       <c r="J90" s="2">
-        <v>45292</v>
+        <v>45261</v>
       </c>
       <c r="K90">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L90">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M90" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>1.060214055930764</v>
+        <v>1.0583104067237841</v>
       </c>
       <c r="B91">
-        <v>6.021405593076401</v>
+        <v>5.8310406723783634</v>
       </c>
       <c r="C91">
         <v>28</v>
@@ -23741,39 +23870,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E91">
-        <v>9.8246443176388158</v>
+        <v>10.03569929372812</v>
       </c>
       <c r="F91">
-        <v>2.247088771873627</v>
+        <v>2.295361182729954</v>
       </c>
       <c r="G91">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H91">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="I91" t="s">
         <v>465</v>
       </c>
       <c r="J91" s="2">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="K91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L91">
         <v>2024</v>
       </c>
       <c r="M91" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>1.054583062225229</v>
+        <v>1.060214055930764</v>
       </c>
       <c r="B92">
-        <v>5.458306222522924</v>
+        <v>6.021405593076401</v>
       </c>
       <c r="C92">
         <v>28</v>
@@ -23782,39 +23911,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E92">
-        <v>9.6179966202026375</v>
+        <v>9.8246443176388158</v>
       </c>
       <c r="F92">
-        <v>2.199824392051887</v>
+        <v>2.247088771873627</v>
       </c>
       <c r="G92">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H92">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="I92" t="s">
         <v>466</v>
       </c>
       <c r="J92" s="2">
-        <v>45352</v>
+        <v>45323</v>
       </c>
       <c r="K92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92">
         <v>2024</v>
       </c>
       <c r="M92" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>1.058171582075532</v>
+        <v>1.054583062225229</v>
       </c>
       <c r="B93">
-        <v>5.8171582075532191</v>
+        <v>5.458306222522924</v>
       </c>
       <c r="C93">
         <v>28</v>
@@ -23823,80 +23952,80 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E93">
-        <v>9.4403327718013941</v>
+        <v>9.6179966202026375</v>
       </c>
       <c r="F93">
-        <v>2.1591891867454178</v>
+        <v>2.199824392051887</v>
       </c>
       <c r="G93">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H93">
-        <v>10.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I93" t="s">
         <v>467</v>
       </c>
       <c r="J93" s="2">
-        <v>45383</v>
+        <v>45352</v>
       </c>
       <c r="K93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L93">
         <v>2024</v>
       </c>
       <c r="M93" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>1.0529610542018479</v>
+        <v>1.058171582075532</v>
       </c>
       <c r="B94">
-        <v>5.2961054201848379</v>
+        <v>5.8171582075532191</v>
       </c>
       <c r="C94">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D94">
-        <v>20.113775177173739</v>
+        <v>19.115832380573561</v>
       </c>
       <c r="E94">
-        <v>9.2109062111873534</v>
+        <v>9.4403327718013941</v>
       </c>
       <c r="F94">
-        <v>2.0537877750908309</v>
+        <v>2.1591891867454178</v>
       </c>
       <c r="G94">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="H94">
-        <v>9.5</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I94" t="s">
         <v>468</v>
       </c>
       <c r="J94" s="2">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="K94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L94">
         <v>2024</v>
       </c>
       <c r="M94" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>1.0518682167925639</v>
+        <v>1.0529610542018479</v>
       </c>
       <c r="B95">
-        <v>5.1868216792563704</v>
+        <v>5.2961054201848379</v>
       </c>
       <c r="C95">
         <v>29</v>
@@ -23905,39 +24034,39 @@
         <v>20.113775177173739</v>
       </c>
       <c r="E95">
-        <v>9.0397689630755789</v>
+        <v>9.2109062111873534</v>
       </c>
       <c r="F95">
-        <v>2.0156287080049289</v>
+        <v>2.0537877750908309</v>
       </c>
       <c r="G95">
         <v>1.1000000000000001</v>
       </c>
       <c r="H95">
-        <v>9.3000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="I95" t="s">
         <v>469</v>
       </c>
       <c r="J95" s="2">
-        <v>45444</v>
+        <v>45413</v>
       </c>
       <c r="K95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L95">
         <v>2024</v>
       </c>
       <c r="M95" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>1.053490836208443</v>
+        <v>1.0518682167925639</v>
       </c>
       <c r="B96">
-        <v>5.3490836208442749</v>
+        <v>5.1868216792563704</v>
       </c>
       <c r="C96">
         <v>29</v>
@@ -23946,80 +24075,80 @@
         <v>20.113775177173739</v>
       </c>
       <c r="E96">
-        <v>8.9122858934584244</v>
+        <v>9.0397689630755789</v>
       </c>
       <c r="F96">
-        <v>1.9872033648402401</v>
+        <v>2.0156287080049289</v>
       </c>
       <c r="G96">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H96">
-        <v>9.4</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I96" t="s">
         <v>470</v>
       </c>
       <c r="J96" s="2">
-        <v>45474</v>
+        <v>45444</v>
       </c>
       <c r="K96">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L96">
         <v>2024</v>
       </c>
       <c r="M96" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>1.049558469047905</v>
+        <v>1.053490836208443</v>
       </c>
       <c r="B97">
-        <v>4.9558469047905396</v>
+        <v>5.3490836208442749</v>
       </c>
       <c r="C97">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D97">
-        <v>18.54899679651448</v>
+        <v>20.113775177173739</v>
       </c>
       <c r="E97">
-        <v>8.2881094746272126</v>
+        <v>8.9122858934584244</v>
       </c>
       <c r="F97">
-        <v>1.924399634609663</v>
+        <v>1.9872033648402401</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H97">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I97" t="s">
         <v>471</v>
       </c>
       <c r="J97" s="2">
-        <v>45505</v>
+        <v>45474</v>
       </c>
       <c r="K97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L97">
         <v>2024</v>
       </c>
       <c r="M97" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>1.048290941446286</v>
+        <v>1.049558469047905</v>
       </c>
       <c r="B98">
-        <v>4.8290941446285984</v>
+        <v>4.9558469047905396</v>
       </c>
       <c r="C98">
         <v>30</v>
@@ -24028,39 +24157,39 @@
         <v>18.54899679651448</v>
       </c>
       <c r="E98">
-        <v>8.1695058802911475</v>
+        <v>8.2881094746272126</v>
       </c>
       <c r="F98">
-        <v>1.8968613022188521</v>
+        <v>1.924399634609663</v>
       </c>
       <c r="G98">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H98">
-        <v>8.6999999999999993</v>
+        <v>8.9</v>
       </c>
       <c r="I98" t="s">
         <v>472</v>
       </c>
       <c r="J98" s="2">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="K98">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L98">
         <v>2024</v>
       </c>
       <c r="M98" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>1.0492600557866141</v>
+        <v>1.048290941446286</v>
       </c>
       <c r="B99">
-        <v>4.9260055786613854</v>
+        <v>4.8290941446285984</v>
       </c>
       <c r="C99">
         <v>30</v>
@@ -24069,80 +24198,80 @@
         <v>18.54899679651448</v>
       </c>
       <c r="E99">
-        <v>8.1060104134661213</v>
+        <v>8.1695058802911475</v>
       </c>
       <c r="F99">
-        <v>1.882118416216741</v>
+        <v>1.8968613022188521</v>
       </c>
       <c r="G99">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H99">
-        <v>8.8000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="I99" t="s">
         <v>473</v>
       </c>
       <c r="J99" s="2">
-        <v>45566</v>
+        <v>45536</v>
       </c>
       <c r="K99">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L99">
         <v>2024</v>
       </c>
       <c r="M99" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>1.048336726448585</v>
+        <v>1.0492600557866141</v>
       </c>
       <c r="B100">
-        <v>4.8336726448585221</v>
+        <v>4.9260055786613854</v>
       </c>
       <c r="C100">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D100">
-        <v>16.984798015414359</v>
+        <v>18.54899679651448</v>
       </c>
       <c r="E100">
-        <v>7.500807113317558</v>
+        <v>8.1060104134661213</v>
       </c>
       <c r="F100">
-        <v>1.8200268888260469</v>
+        <v>1.882118416216741</v>
       </c>
       <c r="G100">
         <v>1.1000000000000001</v>
       </c>
       <c r="H100">
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I100" t="s">
         <v>474</v>
       </c>
       <c r="J100" s="2">
-        <v>45597</v>
+        <v>45566</v>
       </c>
       <c r="K100">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L100">
         <v>2024</v>
       </c>
       <c r="M100" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>1.047960491035139</v>
+        <v>1.048336726448585</v>
       </c>
       <c r="B101">
-        <v>4.7960491035138553</v>
+        <v>4.8336726448585221</v>
       </c>
       <c r="C101">
         <v>31</v>
@@ -24151,39 +24280,39 @@
         <v>16.984798015414359</v>
       </c>
       <c r="E101">
-        <v>7.448935948276743</v>
+        <v>7.500807113317558</v>
       </c>
       <c r="F101">
-        <v>1.807440654611145</v>
+        <v>1.8200268888260469</v>
       </c>
       <c r="G101">
         <v>1.1000000000000001</v>
       </c>
       <c r="H101">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I101" t="s">
         <v>475</v>
       </c>
       <c r="J101" s="2">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="K101">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L101">
         <v>2024</v>
       </c>
       <c r="M101" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>1.0466636254000761</v>
+        <v>1.047960491035139</v>
       </c>
       <c r="B102">
-        <v>4.666362540007607</v>
+        <v>4.7960491035138553</v>
       </c>
       <c r="C102">
         <v>31</v>
@@ -24192,162 +24321,162 @@
         <v>16.984798015414359</v>
       </c>
       <c r="E102">
-        <v>7.4257723047663147</v>
+        <v>7.448935948276743</v>
       </c>
       <c r="F102">
-        <v>1.8018201322599821</v>
+        <v>1.807440654611145</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H102">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="I102" t="s">
         <v>476</v>
       </c>
       <c r="J102" s="2">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="K102">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L102">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="M102" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>1.049197317673384</v>
+        <v>1.0466636254000761</v>
       </c>
       <c r="B103">
-        <v>4.91973176733842</v>
+        <v>4.666362540007607</v>
       </c>
       <c r="C103">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D103">
-        <v>16.566424582675928</v>
+        <v>16.984798015414359</v>
       </c>
       <c r="E103">
-        <v>7.23581369305899</v>
+        <v>7.4257723047663147</v>
       </c>
       <c r="F103">
-        <v>1.777759394342423</v>
+        <v>1.8018201322599821</v>
       </c>
       <c r="G103">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>8.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I103" t="s">
         <v>477</v>
       </c>
       <c r="J103" s="2">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="K103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L103">
         <v>2025</v>
       </c>
       <c r="M103" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>1.047065673072646</v>
+        <v>1.049197317673384</v>
       </c>
       <c r="B104">
-        <v>4.7065673072645966</v>
+        <v>4.91973176733842</v>
       </c>
       <c r="C104">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D104">
-        <v>16.275613713673671</v>
+        <v>16.566424582675928</v>
       </c>
       <c r="E104">
-        <v>7.2776002956687886</v>
+        <v>7.23581369305899</v>
       </c>
       <c r="F104">
-        <v>1.8039292996126619</v>
+        <v>1.777759394342423</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H104">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I104" t="s">
         <v>478</v>
       </c>
       <c r="J104" s="2">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="K104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L104">
         <v>2025</v>
       </c>
       <c r="M104" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>1.0499072887832079</v>
+        <v>1.047065673072646</v>
       </c>
       <c r="B105">
-        <v>4.9907288783208159</v>
+        <v>4.7065673072645966</v>
       </c>
       <c r="C105">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D105">
-        <v>16.298686100020131</v>
+        <v>16.275613713673671</v>
       </c>
       <c r="E105">
-        <v>7.8325390856235746</v>
+        <v>7.2776002956687886</v>
       </c>
       <c r="F105">
-        <v>1.9401096370373889</v>
+        <v>1.8039292996126619</v>
       </c>
       <c r="G105">
         <v>1</v>
       </c>
       <c r="H105">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="I105" t="s">
         <v>479</v>
       </c>
       <c r="J105" s="2">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="K105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L105">
         <v>2025</v>
       </c>
       <c r="M105" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>1.0491555040149549</v>
+        <v>1.0499072887832079</v>
       </c>
       <c r="B106">
-        <v>4.9155504014955156</v>
+        <v>4.9907288783208159</v>
       </c>
       <c r="C106">
         <v>28</v>
@@ -24356,13 +24485,13 @@
         <v>16.298686100020131</v>
       </c>
       <c r="E106">
-        <v>8.0005290532800153</v>
+        <v>7.8325390856235746</v>
       </c>
       <c r="F106">
-        <v>1.9817205312331261</v>
+        <v>1.9401096370373889</v>
       </c>
       <c r="G106">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H106">
         <v>9</v>
@@ -24371,24 +24500,24 @@
         <v>480</v>
       </c>
       <c r="J106" s="2">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="K106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L106">
         <v>2025</v>
       </c>
       <c r="M106" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>1.046409036152032</v>
+        <v>1.0491555040149549</v>
       </c>
       <c r="B107">
-        <v>4.6409036152031957</v>
+        <v>4.9155504014955156</v>
       </c>
       <c r="C107">
         <v>28</v>
@@ -24397,162 +24526,162 @@
         <v>16.298686100020131</v>
       </c>
       <c r="E107">
-        <v>8.2013529230358095</v>
+        <v>8.0005290532800153</v>
       </c>
       <c r="F107">
-        <v>2.031464339824582</v>
+        <v>1.9817205312331261</v>
       </c>
       <c r="G107">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H107">
-        <v>8.8000000000000007</v>
+        <v>9</v>
       </c>
       <c r="I107" t="s">
         <v>481</v>
       </c>
       <c r="J107" s="2">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="K107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L107">
         <v>2025</v>
       </c>
       <c r="M107" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>1.0436198204458811</v>
+        <v>1.046409036152032</v>
       </c>
       <c r="B108">
-        <v>4.3619820445881308</v>
+        <v>4.6409036152031957</v>
       </c>
       <c r="C108">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D108">
-        <v>17.214158003813509</v>
+        <v>16.298686100020131</v>
       </c>
       <c r="E108">
-        <v>8.3198053811383907</v>
+        <v>8.2013529230358095</v>
       </c>
       <c r="F108">
-        <v>2.0052580793959169</v>
+        <v>2.031464339824582</v>
       </c>
       <c r="G108">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H108">
-        <v>8.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I108" t="s">
         <v>482</v>
       </c>
       <c r="J108" s="2">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="K108">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L108">
         <v>2025</v>
       </c>
       <c r="M108" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>1.04191337675469</v>
+        <v>1.0436198204458811</v>
       </c>
       <c r="B109">
-        <v>4.1913376754689544</v>
+        <v>4.3619820445881308</v>
       </c>
       <c r="C109">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109">
-        <v>17.981760321027519</v>
+        <v>17.214158003813509</v>
       </c>
       <c r="E109">
-        <v>8.4258716731015681</v>
+        <v>8.3198053811383907</v>
       </c>
       <c r="F109">
-        <v>1.9870039852828121</v>
+        <v>2.0052580793959169</v>
       </c>
       <c r="G109">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H109">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="I109" t="s">
         <v>483</v>
       </c>
       <c r="J109" s="2">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="K109">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L109">
         <v>2025</v>
       </c>
       <c r="M109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>1.042902221618236</v>
+        <v>1.04191337675469</v>
       </c>
       <c r="B110">
-        <v>4.2902221618235536</v>
+        <v>4.1913376754689544</v>
       </c>
       <c r="C110">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D110">
-        <v>16.78590967293264</v>
+        <v>17.981760321027519</v>
       </c>
       <c r="E110">
-        <v>8.9086299542953977</v>
+        <v>8.4258716731015681</v>
       </c>
       <c r="F110">
-        <v>2.1743951902750132</v>
+        <v>1.9870039852828121</v>
       </c>
       <c r="G110">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H110">
-        <v>8.8000000000000007</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I110" t="s">
         <v>484</v>
       </c>
       <c r="J110" s="2">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="K110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L110">
         <v>2025</v>
       </c>
       <c r="M110" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>1.043161169864792</v>
+        <v>1.042902221618236</v>
       </c>
       <c r="B111">
-        <v>4.3161169864792237</v>
+        <v>4.2902221618235536</v>
       </c>
       <c r="C111">
         <v>28</v>
@@ -24561,80 +24690,80 @@
         <v>16.78590967293264</v>
       </c>
       <c r="E111">
-        <v>9.2046227950215815</v>
+        <v>8.9086299542953977</v>
       </c>
       <c r="F111">
-        <v>2.246640351712045</v>
+        <v>2.1743951902750132</v>
       </c>
       <c r="G111">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="H111">
-        <v>8.9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I111" t="s">
         <v>485</v>
       </c>
       <c r="J111" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="K111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L111">
         <v>2025</v>
       </c>
       <c r="M111" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>1.0458444331058141</v>
+        <v>1.043161169864792</v>
       </c>
       <c r="B112">
-        <v>4.5844433105814097</v>
+        <v>4.3161169864792237</v>
       </c>
       <c r="C112">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D112">
-        <v>15.87606042226448</v>
+        <v>16.78590967293264</v>
       </c>
       <c r="E112">
-        <v>9.5062847480203541</v>
+        <v>9.2046227950215815</v>
       </c>
       <c r="F112">
-        <v>2.3858297368782901</v>
+        <v>2.246640351712045</v>
       </c>
       <c r="G112">
         <v>-0.3</v>
       </c>
       <c r="H112">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="I112" t="s">
         <v>486</v>
       </c>
       <c r="J112" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="K112">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L112">
         <v>2025</v>
       </c>
       <c r="M112" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>1.0475207882271611</v>
+        <v>1.0458444331058141</v>
       </c>
       <c r="B113">
-        <v>4.7520788227160882</v>
+        <v>4.5844433105814097</v>
       </c>
       <c r="C113">
         <v>27</v>
@@ -24643,39 +24772,39 @@
         <v>15.87606042226448</v>
       </c>
       <c r="E113">
-        <v>9.6849617354942694</v>
+        <v>9.5062847480203541</v>
       </c>
       <c r="F113">
-        <v>2.430673004391382</v>
+        <v>2.3858297368782901</v>
       </c>
       <c r="G113">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="H113">
-        <v>9.6999999999999993</v>
+        <v>9.5</v>
       </c>
       <c r="I113" t="s">
         <v>487</v>
       </c>
       <c r="J113" s="2">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="K113">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L113">
         <v>2025</v>
       </c>
       <c r="M113" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>1.04824300899409</v>
+        <v>1.0475207882271611</v>
       </c>
       <c r="B114">
-        <v>4.8243008994089953</v>
+        <v>4.7520788227160882</v>
       </c>
       <c r="C114">
         <v>27</v>
@@ -24684,285 +24813,285 @@
         <v>15.87606042226448</v>
       </c>
       <c r="E114">
-        <v>9.9002650513482813</v>
+        <v>9.6849617354942694</v>
       </c>
       <c r="F114">
-        <v>2.484708525841544</v>
+        <v>2.430673004391382</v>
       </c>
       <c r="G114">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="H114">
-        <v>9.9</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="I114" t="s">
         <v>488</v>
       </c>
       <c r="J114" s="2">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L114">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="M114" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>1.0415464802242049</v>
+        <v>1.04824300899409</v>
       </c>
       <c r="B115">
-        <v>4.1546480224204707</v>
+        <v>4.8243008994089953</v>
       </c>
       <c r="C115">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D115">
-        <v>16.58652366559803</v>
+        <v>15.87606042226448</v>
       </c>
       <c r="E115">
-        <v>10.941750707403999</v>
+        <v>9.9002650513482813</v>
       </c>
       <c r="F115">
-        <v>2.6866378531273671</v>
+        <v>2.484708525841544</v>
       </c>
       <c r="G115">
-        <v>-1.4</v>
+        <v>-0.3</v>
       </c>
       <c r="H115">
-        <v>9.6999999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="I115" t="s">
         <v>489</v>
       </c>
       <c r="J115" s="2">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115">
         <v>2026</v>
       </c>
       <c r="M115" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>0.98384460746823565</v>
+        <v>1.0415464802242049</v>
       </c>
       <c r="B116">
-        <v>-1.615539253176435</v>
+        <v>4.1546480224204707</v>
       </c>
       <c r="C116">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D116">
-        <v>18.99572897372909</v>
+        <v>16.58652366559803</v>
       </c>
       <c r="E116">
-        <v>7.9644924766193963</v>
+        <v>10.941750707403999</v>
       </c>
       <c r="F116">
-        <v>1.8273852877258061</v>
+        <v>2.6866378531273671</v>
       </c>
       <c r="G116">
-        <v>-5.3</v>
+        <v>-1.4</v>
       </c>
       <c r="H116">
-        <v>2.1</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="I116" t="s">
         <v>490</v>
       </c>
       <c r="J116" s="2">
-        <v>44896</v>
+        <v>46054</v>
       </c>
       <c r="K116">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L116">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="M116" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>0.98003625973454445</v>
+        <v>1.0446984253143019</v>
       </c>
       <c r="B117">
-        <v>-1.996374026545555</v>
+        <v>4.4698425314302126</v>
       </c>
       <c r="C117">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D117">
-        <v>21.753475225948449</v>
+        <v>16.58652366559803</v>
       </c>
       <c r="E117">
-        <v>8.7655286035774989</v>
+        <v>11.300311237053259</v>
       </c>
       <c r="F117">
-        <v>1.879376480211949</v>
+        <v>2.7746788181752402</v>
       </c>
       <c r="G117">
-        <v>-5.8</v>
+        <v>-1.2</v>
       </c>
       <c r="H117">
-        <v>1.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I117" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J117" s="2">
-        <v>44927</v>
+        <v>46082</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L117">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="M117" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>0.98029969144219087</v>
+        <v>0.98384460746823565</v>
       </c>
       <c r="B118">
-        <v>-1.970030855780913</v>
+        <v>-1.615539253176435</v>
       </c>
       <c r="C118">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118">
-        <v>21.753475225948449</v>
+        <v>18.99572897372909</v>
       </c>
       <c r="E118">
-        <v>9.0800430922656066</v>
+        <v>7.9644924766193963</v>
       </c>
       <c r="F118">
-        <v>1.9468100782821289</v>
+        <v>1.8273852877258061</v>
       </c>
       <c r="G118">
-        <v>-5.9</v>
+        <v>-5.3</v>
       </c>
       <c r="H118">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I118" t="s">
+        <v>492</v>
+      </c>
+      <c r="J118" s="2">
+        <v>44896</v>
+      </c>
+      <c r="K118">
+        <v>12</v>
+      </c>
+      <c r="L118">
+        <v>2022</v>
+      </c>
+      <c r="M118" t="s">
         <v>493</v>
-      </c>
-      <c r="J118" s="2">
-        <v>44958</v>
-      </c>
-      <c r="K118">
-        <v>2</v>
-      </c>
-      <c r="L118">
-        <v>2023</v>
-      </c>
-      <c r="M118" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>0.99149462050725556</v>
+        <v>0.98003625973454445</v>
       </c>
       <c r="B119">
-        <v>-0.85053794927444359</v>
+        <v>-1.996374026545555</v>
       </c>
       <c r="C119">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D119">
-        <v>20.93488312862889</v>
+        <v>21.753475225948449</v>
       </c>
       <c r="E119">
-        <v>9.3654971767244142</v>
+        <v>8.7655286035774989</v>
       </c>
       <c r="F119">
-        <v>2.0468950083440181</v>
+        <v>1.879376480211949</v>
       </c>
       <c r="G119">
-        <v>-5</v>
+        <v>-5.8</v>
       </c>
       <c r="H119">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="I119" t="s">
         <v>494</v>
       </c>
       <c r="J119" s="2">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="K119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L119">
         <v>2023</v>
       </c>
       <c r="M119" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>0.99872076570122992</v>
+        <v>0.98029969144219087</v>
       </c>
       <c r="B120">
-        <v>-0.12792342987700819</v>
+        <v>-1.970030855780913</v>
       </c>
       <c r="C120">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D120">
-        <v>20.93488312862889</v>
+        <v>21.753475225948449</v>
       </c>
       <c r="E120">
-        <v>9.6014446674081917</v>
+        <v>9.0800430922656066</v>
       </c>
       <c r="F120">
-        <v>2.0984629851207548</v>
+        <v>1.9468100782821289</v>
       </c>
       <c r="G120">
-        <v>-4.4000000000000004</v>
+        <v>-5.9</v>
       </c>
       <c r="H120">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="I120" t="s">
         <v>495</v>
       </c>
       <c r="J120" s="2">
-        <v>45017</v>
+        <v>44958</v>
       </c>
       <c r="K120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L120">
         <v>2023</v>
       </c>
       <c r="M120" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>1.0044133306297109</v>
+        <v>0.99149462050725556</v>
       </c>
       <c r="B121">
-        <v>0.44133306297111652</v>
+        <v>-0.85053794927444359</v>
       </c>
       <c r="C121">
         <v>30</v>
@@ -24971,39 +25100,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E121">
-        <v>9.9851560334364926</v>
+        <v>9.3654971767244142</v>
       </c>
       <c r="F121">
-        <v>2.1823257918620929</v>
+        <v>2.0468950083440181</v>
       </c>
       <c r="G121">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H121">
-        <v>4.9000000000000004</v>
+        <v>3.3</v>
       </c>
       <c r="I121" t="s">
         <v>496</v>
       </c>
       <c r="J121" s="2">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="K121">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L121">
         <v>2023</v>
       </c>
       <c r="M121" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>1.0075035585770851</v>
+        <v>0.99872076570122992</v>
       </c>
       <c r="B122">
-        <v>0.75035585770848456</v>
+        <v>-0.12792342987700819</v>
       </c>
       <c r="C122">
         <v>30</v>
@@ -25012,39 +25141,39 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E122">
-        <v>10.42868041952279</v>
+        <v>9.6014446674081917</v>
       </c>
       <c r="F122">
-        <v>2.2792611530957831</v>
+        <v>2.0984629851207548</v>
       </c>
       <c r="G122">
-        <v>-3.9</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="H122">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="I122" t="s">
         <v>497</v>
       </c>
       <c r="J122" s="2">
-        <v>45078</v>
+        <v>45017</v>
       </c>
       <c r="K122">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L122">
         <v>2023</v>
       </c>
       <c r="M122" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>1.007997804758505</v>
+        <v>1.0044133306297109</v>
       </c>
       <c r="B123">
-        <v>0.79978047585049783</v>
+        <v>0.44133306297111652</v>
       </c>
       <c r="C123">
         <v>30</v>
@@ -25053,121 +25182,121 @@
         <v>20.93488312862889</v>
       </c>
       <c r="E123">
-        <v>10.45284132248816</v>
+        <v>9.9851560334364926</v>
       </c>
       <c r="F123">
-        <v>2.2845416876732552</v>
+        <v>2.1823257918620929</v>
       </c>
       <c r="G123">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="H123">
-        <v>5.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I123" t="s">
         <v>498</v>
       </c>
       <c r="J123" s="2">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="K123">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L123">
         <v>2023</v>
       </c>
       <c r="M123" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>1.024341076751166</v>
+        <v>1.0075035585770851</v>
       </c>
       <c r="B124">
-        <v>2.4341076751166479</v>
+        <v>0.75035585770848456</v>
       </c>
       <c r="C124">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D124">
-        <v>19.980768237809059</v>
+        <v>20.93488312862889</v>
       </c>
       <c r="E124">
-        <v>8.4331466231919983</v>
+        <v>10.42868041952279</v>
       </c>
       <c r="F124">
-        <v>1.886616203385</v>
+        <v>2.2792611530957831</v>
       </c>
       <c r="G124">
-        <v>-1.4</v>
+        <v>-3.9</v>
       </c>
       <c r="H124">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="I124" t="s">
         <v>499</v>
       </c>
       <c r="J124" s="2">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="K124">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L124">
         <v>2023</v>
       </c>
       <c r="M124" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>1.0257114968427059</v>
+        <v>1.007997804758505</v>
       </c>
       <c r="B125">
-        <v>2.5711496842705679</v>
+        <v>0.79978047585049783</v>
       </c>
       <c r="C125">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D125">
-        <v>19.980768237809059</v>
+        <v>20.93488312862889</v>
       </c>
       <c r="E125">
-        <v>8.6942328056947407</v>
+        <v>10.45284132248816</v>
       </c>
       <c r="F125">
-        <v>1.94502493791773</v>
+        <v>2.2845416876732552</v>
       </c>
       <c r="G125">
-        <v>-1.4</v>
+        <v>-3.9</v>
       </c>
       <c r="H125">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="I125" t="s">
         <v>500</v>
       </c>
       <c r="J125" s="2">
-        <v>45170</v>
+        <v>45108</v>
       </c>
       <c r="K125">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L125">
         <v>2023</v>
       </c>
       <c r="M125" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>1.0274341521624779</v>
+        <v>1.024341076751166</v>
       </c>
       <c r="B126">
-        <v>2.7434152162478349</v>
+        <v>2.4341076751166479</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -25176,39 +25305,39 @@
         <v>19.980768237809059</v>
       </c>
       <c r="E126">
-        <v>8.8600899853811086</v>
+        <v>8.4331466231919983</v>
       </c>
       <c r="F126">
-        <v>1.9821295747306971</v>
+        <v>1.886616203385</v>
       </c>
       <c r="G126">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="H126">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I126" t="s">
         <v>501</v>
       </c>
       <c r="J126" s="2">
-        <v>45200</v>
+        <v>45139</v>
       </c>
       <c r="K126">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L126">
         <v>2023</v>
       </c>
       <c r="M126" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>1.0307736875574081</v>
+        <v>1.0257114968427059</v>
       </c>
       <c r="B127">
-        <v>3.077368755740828</v>
+        <v>2.5711496842705679</v>
       </c>
       <c r="C127">
         <v>29</v>
@@ -25217,121 +25346,121 @@
         <v>19.980768237809059</v>
       </c>
       <c r="E127">
-        <v>8.8913866720822945</v>
+        <v>8.6942328056947407</v>
       </c>
       <c r="F127">
-        <v>1.9891310937224751</v>
+        <v>1.94502493791773</v>
       </c>
       <c r="G127">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="H127">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I127" t="s">
         <v>502</v>
       </c>
       <c r="J127" s="2">
-        <v>45231</v>
+        <v>45170</v>
       </c>
       <c r="K127">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L127">
         <v>2023</v>
       </c>
       <c r="M127" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>1.030522934285991</v>
+        <v>1.0274341521624779</v>
       </c>
       <c r="B128">
-        <v>3.0522934285990511</v>
+        <v>2.7434152162478349</v>
       </c>
       <c r="C128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D128">
-        <v>19.115832380573561</v>
+        <v>19.980768237809059</v>
       </c>
       <c r="E128">
-        <v>8.9779628919183239</v>
+        <v>8.8600899853811086</v>
       </c>
       <c r="F128">
-        <v>2.0534361302533419</v>
+        <v>1.9821295747306971</v>
       </c>
       <c r="G128">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="H128">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I128" t="s">
         <v>503</v>
       </c>
       <c r="J128" s="2">
-        <v>45261</v>
+        <v>45200</v>
       </c>
       <c r="K128">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L128">
         <v>2023</v>
       </c>
       <c r="M128" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>1.0362213941757219</v>
+        <v>1.0307736875574081</v>
       </c>
       <c r="B129">
-        <v>3.6221394175722121</v>
+        <v>3.077368755740828</v>
       </c>
       <c r="C129">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D129">
-        <v>19.115832380573561</v>
+        <v>19.980768237809059</v>
       </c>
       <c r="E129">
-        <v>8.9900867178652906</v>
+        <v>8.8913866720822945</v>
       </c>
       <c r="F129">
-        <v>2.0562090869402998</v>
+        <v>1.9891310937224751</v>
       </c>
       <c r="G129">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="H129">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I129" t="s">
         <v>504</v>
       </c>
       <c r="J129" s="2">
-        <v>45292</v>
+        <v>45231</v>
       </c>
       <c r="K129">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L129">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M129" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>1.03982142868727</v>
+        <v>1.030522934285991</v>
       </c>
       <c r="B130">
-        <v>3.9821428687270011</v>
+        <v>3.0522934285990511</v>
       </c>
       <c r="C130">
         <v>28</v>
@@ -25340,39 +25469,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E130">
-        <v>8.9946788840389686</v>
+        <v>8.9779628919183239</v>
       </c>
       <c r="F130">
-        <v>2.0572594053756381</v>
+        <v>2.0534361302533419</v>
       </c>
       <c r="G130">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="H130">
-        <v>8.1999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="I130" t="s">
         <v>505</v>
       </c>
       <c r="J130" s="2">
-        <v>45323</v>
+        <v>45261</v>
       </c>
       <c r="K130">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L130">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M130" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>1.0401978445851581</v>
+        <v>1.0362213941757219</v>
       </c>
       <c r="B131">
-        <v>4.0197844585157627</v>
+        <v>3.6221394175722121</v>
       </c>
       <c r="C131">
         <v>28</v>
@@ -25381,39 +25510,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E131">
-        <v>8.9640688418837513</v>
+        <v>8.9900867178652906</v>
       </c>
       <c r="F131">
-        <v>2.050258288611535</v>
+        <v>2.0562090869402998</v>
       </c>
       <c r="G131">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="H131">
-        <v>8.1999999999999993</v>
+        <v>7.8</v>
       </c>
       <c r="I131" t="s">
         <v>506</v>
       </c>
       <c r="J131" s="2">
-        <v>45352</v>
+        <v>45292</v>
       </c>
       <c r="K131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L131">
         <v>2024</v>
       </c>
       <c r="M131" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>1.0443954521737191</v>
+        <v>1.03982142868727</v>
       </c>
       <c r="B132">
-        <v>4.4395452173719319</v>
+        <v>3.9821428687270011</v>
       </c>
       <c r="C132">
         <v>28</v>
@@ -25422,39 +25551,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E132">
-        <v>8.9378341367699115</v>
+        <v>8.9946788840389686</v>
       </c>
       <c r="F132">
-        <v>2.0442578972091829</v>
+        <v>2.0572594053756381</v>
       </c>
       <c r="G132">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="H132">
-        <v>8.6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I132" t="s">
         <v>507</v>
       </c>
       <c r="J132" s="2">
-        <v>45383</v>
+        <v>45323</v>
       </c>
       <c r="K132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L132">
         <v>2024</v>
       </c>
       <c r="M132" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>1.0487346955015411</v>
+        <v>1.0401978445851581</v>
       </c>
       <c r="B133">
-        <v>4.8734695501540637</v>
+        <v>4.0197844585157627</v>
       </c>
       <c r="C133">
         <v>28</v>
@@ -25463,39 +25592,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E133">
-        <v>8.7935093785894285</v>
+        <v>8.9640688418837513</v>
       </c>
       <c r="F133">
-        <v>2.0112479954635809</v>
+        <v>2.050258288611535</v>
       </c>
       <c r="G133">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="H133">
-        <v>9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I133" t="s">
         <v>508</v>
       </c>
       <c r="J133" s="2">
-        <v>45413</v>
+        <v>45352</v>
       </c>
       <c r="K133">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L133">
         <v>2024</v>
       </c>
       <c r="M133" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>1.0504436225967599</v>
+        <v>1.0443954521737191</v>
       </c>
       <c r="B134">
-        <v>5.0443622596760376</v>
+        <v>4.4395452173719319</v>
       </c>
       <c r="C134">
         <v>28</v>
@@ -25504,39 +25633,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E134">
-        <v>8.626379275414136</v>
+        <v>8.9378341367699115</v>
       </c>
       <c r="F134">
-        <v>1.9730220642089491</v>
+        <v>2.0442578972091829</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H134">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I134" t="s">
         <v>509</v>
       </c>
       <c r="J134" s="2">
-        <v>45444</v>
+        <v>45383</v>
       </c>
       <c r="K134">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L134">
         <v>2024</v>
       </c>
       <c r="M134" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>1.049163711236947</v>
+        <v>1.0487346955015411</v>
       </c>
       <c r="B135">
-        <v>4.9163711236947183</v>
+        <v>4.8734695501540637</v>
       </c>
       <c r="C135">
         <v>28</v>
@@ -25545,39 +25674,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E135">
-        <v>8.5202275513698087</v>
+        <v>8.7935093785894285</v>
       </c>
       <c r="F135">
-        <v>1.948743083769241</v>
+        <v>2.0112479954635809</v>
       </c>
       <c r="G135">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H135">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I135" t="s">
         <v>510</v>
       </c>
       <c r="J135" s="2">
-        <v>45474</v>
+        <v>45413</v>
       </c>
       <c r="K135">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L135">
         <v>2024</v>
       </c>
       <c r="M135" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>1.0490817571221689</v>
+        <v>1.0504436225967599</v>
       </c>
       <c r="B136">
-        <v>4.9081757122169334</v>
+        <v>5.0443622596760376</v>
       </c>
       <c r="C136">
         <v>28</v>
@@ -25586,39 +25715,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E136">
-        <v>8.4586446883490325</v>
+        <v>8.626379275414136</v>
       </c>
       <c r="F136">
-        <v>1.9346578756375461</v>
+        <v>1.9730220642089491</v>
       </c>
       <c r="G136">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="I136" t="s">
         <v>511</v>
       </c>
       <c r="J136" s="2">
-        <v>45505</v>
+        <v>45444</v>
       </c>
       <c r="K136">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L136">
         <v>2024</v>
       </c>
       <c r="M136" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>1.049707657347035</v>
+        <v>1.049163711236947</v>
       </c>
       <c r="B137">
-        <v>4.9707657347034973</v>
+        <v>4.9163711236947183</v>
       </c>
       <c r="C137">
         <v>28</v>
@@ -25627,13 +25756,13 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E137">
-        <v>8.4510791752975436</v>
+        <v>8.5202275513698087</v>
       </c>
       <c r="F137">
-        <v>1.932927494477493</v>
+        <v>1.948743083769241</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H137">
         <v>8.9</v>
@@ -25642,24 +25771,24 @@
         <v>512</v>
       </c>
       <c r="J137" s="2">
-        <v>45536</v>
+        <v>45474</v>
       </c>
       <c r="K137">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L137">
         <v>2024</v>
       </c>
       <c r="M137" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>1.0495413705020109</v>
+        <v>1.0490817571221689</v>
       </c>
       <c r="B138">
-        <v>4.9541370502011128</v>
+        <v>4.9081757122169334</v>
       </c>
       <c r="C138">
         <v>28</v>
@@ -25668,13 +25797,13 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E138">
-        <v>8.4762146436878592</v>
+        <v>8.4586446883490325</v>
       </c>
       <c r="F138">
-        <v>1.938676468890161</v>
+        <v>1.9346578756375461</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H138">
         <v>8.9</v>
@@ -25683,24 +25812,24 @@
         <v>513</v>
       </c>
       <c r="J138" s="2">
-        <v>45566</v>
+        <v>45505</v>
       </c>
       <c r="K138">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L138">
         <v>2024</v>
       </c>
       <c r="M138" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>1.049938707404132</v>
+        <v>1.049707657347035</v>
       </c>
       <c r="B139">
-        <v>4.9938707404132421</v>
+        <v>4.9707657347034973</v>
       </c>
       <c r="C139">
         <v>28</v>
@@ -25709,39 +25838,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E139">
-        <v>8.5214008501954499</v>
+        <v>8.4510791752975436</v>
       </c>
       <c r="F139">
-        <v>1.9490114402137</v>
+        <v>1.932927494477493</v>
       </c>
       <c r="G139">
         <v>1</v>
       </c>
       <c r="H139">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I139" t="s">
         <v>514</v>
       </c>
       <c r="J139" s="2">
-        <v>45597</v>
+        <v>45536</v>
       </c>
       <c r="K139">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L139">
         <v>2024</v>
       </c>
       <c r="M139" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>1.0507794398533561</v>
+        <v>1.0495413705020109</v>
       </c>
       <c r="B140">
-        <v>5.077943985335609</v>
+        <v>4.9541370502011128</v>
       </c>
       <c r="C140">
         <v>28</v>
@@ -25750,39 +25879,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E140">
-        <v>8.5272884004097076</v>
+        <v>8.4762146436878592</v>
       </c>
       <c r="F140">
-        <v>1.950358038375686</v>
+        <v>1.938676468890161</v>
       </c>
       <c r="G140">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="I140" t="s">
         <v>515</v>
       </c>
       <c r="J140" s="2">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="K140">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L140">
         <v>2024</v>
       </c>
       <c r="M140" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>1.052900083662393</v>
+        <v>1.049938707404132</v>
       </c>
       <c r="B141">
-        <v>5.2900083662393182</v>
+        <v>4.9938707404132421</v>
       </c>
       <c r="C141">
         <v>28</v>
@@ -25791,39 +25920,39 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E141">
-        <v>8.4562235630387086</v>
+        <v>8.5214008501954499</v>
       </c>
       <c r="F141">
-        <v>1.9341041168118589</v>
+        <v>1.9490114402137</v>
       </c>
       <c r="G141">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>9.3000000000000007</v>
+        <v>9</v>
       </c>
       <c r="I141" t="s">
         <v>516</v>
       </c>
       <c r="J141" s="2">
-        <v>45658</v>
+        <v>45597</v>
       </c>
       <c r="K141">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L141">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="M141" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>1.054918176709073</v>
+        <v>1.0507794398533561</v>
       </c>
       <c r="B142">
-        <v>5.4918176709073174</v>
+        <v>5.077943985335609</v>
       </c>
       <c r="C142">
         <v>28</v>
@@ -25832,121 +25961,121 @@
         <v>19.115832380573561</v>
       </c>
       <c r="E142">
-        <v>8.4158643751521183</v>
+        <v>8.5272884004097076</v>
       </c>
       <c r="F142">
-        <v>1.9248731792827449</v>
+        <v>1.950358038375686</v>
       </c>
       <c r="G142">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H142">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I142" t="s">
         <v>517</v>
       </c>
       <c r="J142" s="2">
-        <v>45689</v>
+        <v>45627</v>
       </c>
       <c r="K142">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L142">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="M142" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>1.0562252248529671</v>
+        <v>1.052900083662393</v>
       </c>
       <c r="B143">
-        <v>5.6225224852967326</v>
+        <v>5.2900083662393182</v>
       </c>
       <c r="C143">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D143">
-        <v>18.529494333301809</v>
+        <v>19.115832380573561</v>
       </c>
       <c r="E143">
-        <v>8.130541975380206</v>
+        <v>8.4562235630387086</v>
       </c>
       <c r="F143">
-        <v>1.8888075604391961</v>
+        <v>1.9341041168118589</v>
       </c>
       <c r="G143">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="H143">
-        <v>9.5</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I143" t="s">
         <v>518</v>
       </c>
       <c r="J143" s="2">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="K143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L143">
         <v>2025</v>
       </c>
       <c r="M143" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>1.056258611903089</v>
+        <v>1.054918176709073</v>
       </c>
       <c r="B144">
-        <v>5.625861190308945</v>
+        <v>5.4918176709073174</v>
       </c>
       <c r="C144">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D144">
-        <v>18.529494333301809</v>
+        <v>19.115832380573561</v>
       </c>
       <c r="E144">
-        <v>8.1072813168525517</v>
+        <v>8.4158643751521183</v>
       </c>
       <c r="F144">
-        <v>1.883403872982583</v>
+        <v>1.9248731792827449</v>
       </c>
       <c r="G144">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H144">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I144" t="s">
         <v>519</v>
       </c>
       <c r="J144" s="2">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="K144">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L144">
         <v>2025</v>
       </c>
       <c r="M144" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>1.0557291021032189</v>
+        <v>1.0562252248529671</v>
       </c>
       <c r="B145">
-        <v>5.5729102103218908</v>
+        <v>5.6225224852967326</v>
       </c>
       <c r="C145">
         <v>27</v>
@@ -25955,10 +26084,10 @@
         <v>18.529494333301809</v>
       </c>
       <c r="E145">
-        <v>8.1861358910509114</v>
+        <v>8.130541975380206</v>
       </c>
       <c r="F145">
-        <v>1.9017225922478029</v>
+        <v>1.8888075604391961</v>
       </c>
       <c r="G145">
         <v>1.7</v>
@@ -25970,24 +26099,24 @@
         <v>520</v>
       </c>
       <c r="J145" s="2">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="K145">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L145">
         <v>2025</v>
       </c>
       <c r="M145" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>1.055317824332328</v>
+        <v>1.056258611903089</v>
       </c>
       <c r="B146">
-        <v>5.5317824332327792</v>
+        <v>5.625861190308945</v>
       </c>
       <c r="C146">
         <v>27</v>
@@ -25996,13 +26125,13 @@
         <v>18.529494333301809</v>
       </c>
       <c r="E146">
-        <v>8.2356193782576277</v>
+        <v>8.1072813168525517</v>
       </c>
       <c r="F146">
-        <v>1.9132181094022509</v>
+        <v>1.883403872982583</v>
       </c>
       <c r="G146">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H146">
         <v>9.5</v>
@@ -26011,24 +26140,24 @@
         <v>521</v>
       </c>
       <c r="J146" s="2">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="K146">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L146">
         <v>2025</v>
       </c>
       <c r="M146" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>1.0562171260140769</v>
+        <v>1.0557291021032189</v>
       </c>
       <c r="B147">
-        <v>5.621712601407669</v>
+        <v>5.5729102103218908</v>
       </c>
       <c r="C147">
         <v>27</v>
@@ -26037,39 +26166,39 @@
         <v>18.529494333301809</v>
       </c>
       <c r="E147">
-        <v>8.301435937395059</v>
+        <v>8.1861358910509114</v>
       </c>
       <c r="F147">
-        <v>1.9285079652171899</v>
+        <v>1.9017225922478029</v>
       </c>
       <c r="G147">
         <v>1.7</v>
       </c>
       <c r="H147">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I147" t="s">
         <v>522</v>
       </c>
       <c r="J147" s="2">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="K147">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L147">
         <v>2025</v>
       </c>
       <c r="M147" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>1.0558351583267911</v>
+        <v>1.055317824332328</v>
       </c>
       <c r="B148">
-        <v>5.5835158326790868</v>
+        <v>5.5317824332327792</v>
       </c>
       <c r="C148">
         <v>27</v>
@@ -26078,39 +26207,39 @@
         <v>18.529494333301809</v>
       </c>
       <c r="E148">
-        <v>8.3454114615585588</v>
+        <v>8.2356193782576277</v>
       </c>
       <c r="F148">
-        <v>1.9387239265597189</v>
+        <v>1.9132181094022509</v>
       </c>
       <c r="G148">
         <v>1.6</v>
       </c>
       <c r="H148">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I148" t="s">
         <v>523</v>
       </c>
       <c r="J148" s="2">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="K148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L148">
         <v>2025</v>
       </c>
       <c r="M148" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>1.0553299450435929</v>
+        <v>1.0562171260140769</v>
       </c>
       <c r="B149">
-        <v>5.5329945043593121</v>
+        <v>5.621712601407669</v>
       </c>
       <c r="C149">
         <v>27</v>
@@ -26119,13 +26248,13 @@
         <v>18.529494333301809</v>
       </c>
       <c r="E149">
-        <v>8.4357280447285881</v>
+        <v>8.301435937395059</v>
       </c>
       <c r="F149">
-        <v>1.95970538703814</v>
+        <v>1.9285079652171899</v>
       </c>
       <c r="G149">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H149">
         <v>9.6</v>
@@ -26134,106 +26263,106 @@
         <v>524</v>
       </c>
       <c r="J149" s="2">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="K149">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L149">
         <v>2025</v>
       </c>
       <c r="M149" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>1.0537179403362831</v>
+        <v>1.0558351583267911</v>
       </c>
       <c r="B150">
-        <v>5.3717940336283299</v>
+        <v>5.5835158326790868</v>
       </c>
       <c r="C150">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D150">
-        <v>14.264404329923959</v>
+        <v>18.529494333301809</v>
       </c>
       <c r="E150">
-        <v>8.1755582062632914</v>
+        <v>8.3454114615585588</v>
       </c>
       <c r="F150">
-        <v>2.1646644984973351</v>
+        <v>1.9387239265597189</v>
       </c>
       <c r="G150">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="H150">
-        <v>9.8000000000000007</v>
+        <v>9.6</v>
       </c>
       <c r="I150" t="s">
         <v>525</v>
       </c>
       <c r="J150" s="2">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="K150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L150">
         <v>2025</v>
       </c>
       <c r="M150" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>1.0525045781797799</v>
+        <v>1.0553299450435929</v>
       </c>
       <c r="B151">
-        <v>5.2504578179779724</v>
+        <v>5.5329945043593121</v>
       </c>
       <c r="C151">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D151">
-        <v>14.264404329923959</v>
+        <v>18.529494333301809</v>
       </c>
       <c r="E151">
-        <v>8.2699452226860437</v>
+        <v>8.4357280447285881</v>
       </c>
       <c r="F151">
-        <v>2.189655602274553</v>
+        <v>1.95970538703814</v>
       </c>
       <c r="G151">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="H151">
-        <v>9.8000000000000007</v>
+        <v>9.6</v>
       </c>
       <c r="I151" t="s">
         <v>526</v>
       </c>
       <c r="J151" s="2">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="K151">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L151">
         <v>2025</v>
       </c>
       <c r="M151" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>1.052936843883328</v>
+        <v>1.0537179403362831</v>
       </c>
       <c r="B152">
-        <v>5.2936843883327764</v>
+        <v>5.3717940336283299</v>
       </c>
       <c r="C152">
         <v>25</v>
@@ -26242,39 +26371,39 @@
         <v>14.264404329923959</v>
       </c>
       <c r="E152">
-        <v>8.3834858988564651</v>
+        <v>8.1755582062632914</v>
       </c>
       <c r="F152">
-        <v>2.219718071972733</v>
+        <v>2.1646644984973351</v>
       </c>
       <c r="G152">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H152">
-        <v>9.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I152" t="s">
         <v>527</v>
       </c>
       <c r="J152" s="2">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="K152">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L152">
         <v>2025</v>
       </c>
       <c r="M152" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>1.052368708628463</v>
+        <v>1.0525045781797799</v>
       </c>
       <c r="B153">
-        <v>5.2368708628463434</v>
+        <v>5.2504578179779724</v>
       </c>
       <c r="C153">
         <v>25</v>
@@ -26283,39 +26412,39 @@
         <v>14.264404329923959</v>
       </c>
       <c r="E153">
-        <v>8.5287262546485785</v>
+        <v>8.2699452226860437</v>
       </c>
       <c r="F153">
-        <v>2.258173750961288</v>
+        <v>2.189655602274553</v>
       </c>
       <c r="G153">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H153">
-        <v>9.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I153" t="s">
         <v>528</v>
       </c>
       <c r="J153" s="2">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="K153">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L153">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="M153" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>1.0516513521833919</v>
+        <v>1.052936843883328</v>
       </c>
       <c r="B154">
-        <v>5.1651352183391896</v>
+        <v>5.2936843883327764</v>
       </c>
       <c r="C154">
         <v>25</v>
@@ -26324,13 +26453,13 @@
         <v>14.264404329923959</v>
       </c>
       <c r="E154">
-        <v>8.6788797117843117</v>
+        <v>8.3834858988564651</v>
       </c>
       <c r="F154">
-        <v>2.297930284984782</v>
+        <v>2.219718071972733</v>
       </c>
       <c r="G154">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H154">
         <v>9.9</v>
@@ -26339,16 +26468,139 @@
         <v>529</v>
       </c>
       <c r="J154" s="2">
+        <v>45992</v>
+      </c>
+      <c r="K154">
+        <v>12</v>
+      </c>
+      <c r="L154">
+        <v>2025</v>
+      </c>
+      <c r="M154" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>1.052368708628463</v>
+      </c>
+      <c r="B155">
+        <v>5.2368708628463434</v>
+      </c>
+      <c r="C155">
+        <v>25</v>
+      </c>
+      <c r="D155">
+        <v>14.264404329923959</v>
+      </c>
+      <c r="E155">
+        <v>8.5287262546485785</v>
+      </c>
+      <c r="F155">
+        <v>2.258173750961288</v>
+      </c>
+      <c r="G155">
+        <v>0.6</v>
+      </c>
+      <c r="H155">
+        <v>9.9</v>
+      </c>
+      <c r="I155" t="s">
+        <v>530</v>
+      </c>
+      <c r="J155" s="2">
+        <v>46023</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>2026</v>
+      </c>
+      <c r="M155" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>1.0516513521833919</v>
+      </c>
+      <c r="B156">
+        <v>5.1651352183391896</v>
+      </c>
+      <c r="C156">
+        <v>25</v>
+      </c>
+      <c r="D156">
+        <v>14.264404329923959</v>
+      </c>
+      <c r="E156">
+        <v>8.6788797117843117</v>
+      </c>
+      <c r="F156">
+        <v>2.297930284984782</v>
+      </c>
+      <c r="G156">
+        <v>0.4</v>
+      </c>
+      <c r="H156">
+        <v>9.9</v>
+      </c>
+      <c r="I156" t="s">
+        <v>531</v>
+      </c>
+      <c r="J156" s="2">
         <v>46054</v>
       </c>
-      <c r="K154">
+      <c r="K156">
         <v>2</v>
       </c>
-      <c r="L154">
+      <c r="L156">
         <v>2026</v>
       </c>
-      <c r="M154" t="s">
-        <v>491</v>
+      <c r="M156" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>1.049822228811077</v>
+      </c>
+      <c r="B157">
+        <v>4.9822228811077007</v>
+      </c>
+      <c r="C157">
+        <v>25</v>
+      </c>
+      <c r="D157">
+        <v>14.264404329923959</v>
+      </c>
+      <c r="E157">
+        <v>8.8847343608160347</v>
+      </c>
+      <c r="F157">
+        <v>2.3524349731500771</v>
+      </c>
+      <c r="G157">
+        <v>0.1</v>
+      </c>
+      <c r="H157">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I157" t="s">
+        <v>532</v>
+      </c>
+      <c r="J157" s="2">
+        <v>46082</v>
+      </c>
+      <c r="K157">
+        <v>3</v>
+      </c>
+      <c r="L157">
+        <v>2026</v>
+      </c>
+      <c r="M157" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
